--- a/PRC_National_dataset.xlsx
+++ b/PRC_National_dataset.xlsx
@@ -479,11 +479,14 @@
       <c r="E2">
         <v>1384</v>
       </c>
+      <c r="F2">
+        <v>1339</v>
+      </c>
       <c r="G2">
-        <v>2329</v>
+        <v>2396</v>
       </c>
       <c r="H2">
-        <v>12012</v>
+        <v>12223</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -502,11 +505,14 @@
       <c r="E3">
         <v>1500</v>
       </c>
+      <c r="F3">
+        <v>1306</v>
+      </c>
       <c r="G3">
-        <v>2415</v>
+        <v>2501</v>
       </c>
       <c r="H3">
-        <v>12281</v>
+        <v>12561</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -525,11 +531,14 @@
       <c r="E4">
         <v>1615</v>
       </c>
+      <c r="F4">
+        <v>1440</v>
+      </c>
       <c r="G4">
-        <v>2468</v>
+        <v>2522</v>
       </c>
       <c r="H4">
-        <v>12448</v>
+        <v>12653</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -548,11 +557,14 @@
       <c r="E5">
         <v>1579</v>
       </c>
+      <c r="F5">
+        <v>1475</v>
+      </c>
       <c r="G5">
-        <v>2450</v>
+        <v>2488</v>
       </c>
       <c r="H5">
-        <v>12692</v>
+        <v>12843</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -571,11 +583,14 @@
       <c r="E6">
         <v>1609</v>
       </c>
+      <c r="F6">
+        <v>1412</v>
+      </c>
       <c r="G6">
-        <v>2434</v>
+        <v>2490</v>
       </c>
       <c r="H6">
-        <v>12951</v>
+        <v>13142</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -594,11 +609,14 @@
       <c r="E7">
         <v>1672</v>
       </c>
+      <c r="F7">
+        <v>1430</v>
+      </c>
       <c r="G7">
-        <v>2561</v>
+        <v>2619</v>
       </c>
       <c r="H7">
-        <v>12959</v>
+        <v>13150</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -617,11 +635,14 @@
       <c r="E8">
         <v>1653</v>
       </c>
+      <c r="F8">
+        <v>1376</v>
+      </c>
       <c r="G8">
-        <v>2550</v>
+        <v>2581</v>
       </c>
       <c r="H8">
-        <v>13175</v>
+        <v>13314</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -640,11 +661,14 @@
       <c r="E9">
         <v>1687</v>
       </c>
+      <c r="F9">
+        <v>1355</v>
+      </c>
       <c r="G9">
-        <v>2627</v>
+        <v>2649</v>
       </c>
       <c r="H9">
-        <v>13027</v>
+        <v>13106</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -663,11 +687,14 @@
       <c r="E10">
         <v>1732</v>
       </c>
+      <c r="F10">
+        <v>1584</v>
+      </c>
       <c r="G10">
-        <v>2759</v>
+        <v>2792</v>
       </c>
       <c r="H10">
-        <v>13601</v>
+        <v>13679</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -686,11 +713,14 @@
       <c r="E11">
         <v>1722</v>
       </c>
+      <c r="F11">
+        <v>1375</v>
+      </c>
       <c r="G11">
-        <v>2726</v>
+        <v>2733</v>
       </c>
       <c r="H11">
-        <v>13729</v>
+        <v>13740</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -709,11 +739,14 @@
       <c r="E12">
         <v>1647</v>
       </c>
+      <c r="F12">
+        <v>1477</v>
+      </c>
       <c r="G12">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="H12">
-        <v>13442</v>
+        <v>13449</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -732,6 +765,9 @@
       <c r="E13">
         <v>1627</v>
       </c>
+      <c r="F13">
+        <v>1382</v>
+      </c>
       <c r="G13">
         <v>2873</v>
       </c>
@@ -755,11 +791,14 @@
       <c r="E14">
         <v>1812</v>
       </c>
+      <c r="F14">
+        <v>1430</v>
+      </c>
       <c r="G14">
-        <v>2759</v>
+        <v>2762</v>
       </c>
       <c r="H14">
-        <v>14133</v>
+        <v>14141</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -778,11 +817,14 @@
       <c r="E15">
         <v>1873</v>
       </c>
+      <c r="F15">
+        <v>1480</v>
+      </c>
       <c r="G15">
-        <v>2898</v>
+        <v>2899</v>
       </c>
       <c r="H15">
-        <v>14476</v>
+        <v>14482</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -801,11 +843,14 @@
       <c r="E16">
         <v>1127</v>
       </c>
+      <c r="F16">
+        <v>1049</v>
+      </c>
       <c r="G16">
-        <v>1865</v>
+        <v>1914</v>
       </c>
       <c r="H16">
-        <v>9623</v>
+        <v>9789</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -824,11 +869,14 @@
       <c r="E17">
         <v>1237</v>
       </c>
+      <c r="F17">
+        <v>1013</v>
+      </c>
       <c r="G17">
-        <v>1929</v>
+        <v>1994</v>
       </c>
       <c r="H17">
-        <v>9842</v>
+        <v>10067</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -847,11 +895,14 @@
       <c r="E18">
         <v>1301</v>
       </c>
+      <c r="F18">
+        <v>1130</v>
+      </c>
       <c r="G18">
-        <v>1976</v>
+        <v>2017</v>
       </c>
       <c r="H18">
-        <v>9966</v>
+        <v>10119</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -870,11 +921,14 @@
       <c r="E19">
         <v>1274</v>
       </c>
+      <c r="F19">
+        <v>1191</v>
+      </c>
       <c r="G19">
-        <v>1967</v>
+        <v>1998</v>
       </c>
       <c r="H19">
-        <v>10202</v>
+        <v>10322</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -893,11 +947,14 @@
       <c r="E20">
         <v>1317</v>
       </c>
+      <c r="F20">
+        <v>1094</v>
+      </c>
       <c r="G20">
-        <v>1934</v>
+        <v>1979</v>
       </c>
       <c r="H20">
-        <v>10405</v>
+        <v>10555</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -916,11 +973,14 @@
       <c r="E21">
         <v>1338</v>
       </c>
+      <c r="F21">
+        <v>1116</v>
+      </c>
       <c r="G21">
-        <v>2035</v>
+        <v>2080</v>
       </c>
       <c r="H21">
-        <v>10406</v>
+        <v>10556</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -939,11 +999,14 @@
       <c r="E22">
         <v>1343</v>
       </c>
+      <c r="F22">
+        <v>1081</v>
+      </c>
       <c r="G22">
-        <v>2005</v>
+        <v>2028</v>
       </c>
       <c r="H22">
-        <v>10512</v>
+        <v>10624</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -962,11 +1025,14 @@
       <c r="E23">
         <v>1391</v>
       </c>
+      <c r="F23">
+        <v>1034</v>
+      </c>
       <c r="G23">
-        <v>2054</v>
+        <v>2071</v>
       </c>
       <c r="H23">
-        <v>10330</v>
+        <v>10394</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -985,11 +1051,14 @@
       <c r="E24">
         <v>1364</v>
       </c>
+      <c r="F24">
+        <v>1215</v>
+      </c>
       <c r="G24">
-        <v>2174</v>
+        <v>2201</v>
       </c>
       <c r="H24">
-        <v>10738</v>
+        <v>10804</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1008,11 +1077,14 @@
       <c r="E25">
         <v>1378</v>
       </c>
+      <c r="F25">
+        <v>1079</v>
+      </c>
       <c r="G25">
-        <v>2131</v>
+        <v>2138</v>
       </c>
       <c r="H25">
-        <v>10827</v>
+        <v>10837</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1031,11 +1103,14 @@
       <c r="E26">
         <v>1311</v>
       </c>
+      <c r="F26">
+        <v>1144</v>
+      </c>
       <c r="G26">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="H26">
-        <v>10489</v>
+        <v>10494</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1054,6 +1129,9 @@
       <c r="E27">
         <v>1307</v>
       </c>
+      <c r="F27">
+        <v>1067</v>
+      </c>
       <c r="G27">
         <v>2067</v>
       </c>
@@ -1077,11 +1155,14 @@
       <c r="E28">
         <v>1433</v>
       </c>
+      <c r="F28">
+        <v>1099</v>
+      </c>
       <c r="G28">
-        <v>1985</v>
+        <v>1988</v>
       </c>
       <c r="H28">
-        <v>10621</v>
+        <v>10628</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1100,11 +1181,14 @@
       <c r="E29">
         <v>1476</v>
       </c>
+      <c r="F29">
+        <v>1121</v>
+      </c>
       <c r="G29">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="H29">
-        <v>10756</v>
+        <v>10761</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1123,11 +1207,14 @@
       <c r="E30">
         <v>257</v>
       </c>
+      <c r="F30">
+        <v>290</v>
+      </c>
       <c r="G30">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="H30">
-        <v>2389</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1146,11 +1233,14 @@
       <c r="E31">
         <v>263</v>
       </c>
+      <c r="F31">
+        <v>293</v>
+      </c>
       <c r="G31">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="H31">
-        <v>2439</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1169,11 +1259,14 @@
       <c r="E32">
         <v>314</v>
       </c>
+      <c r="F32">
+        <v>310</v>
+      </c>
       <c r="G32">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="H32">
-        <v>2482</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1192,11 +1285,14 @@
       <c r="E33">
         <v>305</v>
       </c>
+      <c r="F33">
+        <v>284</v>
+      </c>
       <c r="G33">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="H33">
-        <v>2490</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1215,11 +1311,14 @@
       <c r="E34">
         <v>292</v>
       </c>
+      <c r="F34">
+        <v>318</v>
+      </c>
       <c r="G34">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="H34">
-        <v>2546</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1238,11 +1337,14 @@
       <c r="E35">
         <v>334</v>
       </c>
+      <c r="F35">
+        <v>314</v>
+      </c>
       <c r="G35">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="H35">
-        <v>2553</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1261,11 +1363,14 @@
       <c r="E36">
         <v>310</v>
       </c>
+      <c r="F36">
+        <v>295</v>
+      </c>
       <c r="G36">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="H36">
-        <v>2663</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1284,11 +1389,14 @@
       <c r="E37">
         <v>296</v>
       </c>
+      <c r="F37">
+        <v>321</v>
+      </c>
       <c r="G37">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="H37">
-        <v>2697</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1307,11 +1415,14 @@
       <c r="E38">
         <v>368</v>
       </c>
+      <c r="F38">
+        <v>369</v>
+      </c>
       <c r="G38">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="H38">
-        <v>2863</v>
+        <v>2875</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1330,11 +1441,14 @@
       <c r="E39">
         <v>344</v>
       </c>
+      <c r="F39">
+        <v>296</v>
+      </c>
       <c r="G39">
         <v>595</v>
       </c>
       <c r="H39">
-        <v>2902</v>
+        <v>2903</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1353,11 +1467,14 @@
       <c r="E40">
         <v>336</v>
       </c>
+      <c r="F40">
+        <v>333</v>
+      </c>
       <c r="G40">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H40">
-        <v>2953</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1376,6 +1493,9 @@
       <c r="E41">
         <v>320</v>
       </c>
+      <c r="F41">
+        <v>315</v>
+      </c>
       <c r="G41">
         <v>806</v>
       </c>
@@ -1399,11 +1519,14 @@
       <c r="E42">
         <v>379</v>
       </c>
+      <c r="F42">
+        <v>331</v>
+      </c>
       <c r="G42">
         <v>774</v>
       </c>
       <c r="H42">
-        <v>3512</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1422,11 +1545,14 @@
       <c r="E43">
         <v>397</v>
       </c>
+      <c r="F43">
+        <v>359</v>
+      </c>
       <c r="G43">
         <v>814</v>
       </c>
       <c r="H43">
-        <v>3720</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1565,10 +1691,10 @@
         <v>1687</v>
       </c>
       <c r="G51">
-        <v>2299</v>
+        <v>2308</v>
       </c>
       <c r="H51">
-        <v>12203</v>
+        <v>12257</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1588,10 +1714,10 @@
         <v>1732</v>
       </c>
       <c r="G52">
-        <v>2398</v>
+        <v>2414</v>
       </c>
       <c r="H52">
-        <v>12696</v>
+        <v>12750</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1611,10 +1737,10 @@
         <v>1722</v>
       </c>
       <c r="G53">
-        <v>2375</v>
+        <v>2378</v>
       </c>
       <c r="H53">
-        <v>12813</v>
+        <v>12818</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1637,7 +1763,7 @@
         <v>1979</v>
       </c>
       <c r="H54">
-        <v>12590</v>
+        <v>12593</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -1680,10 +1806,10 @@
         <v>1812</v>
       </c>
       <c r="G56">
-        <v>2398</v>
+        <v>2401</v>
       </c>
       <c r="H56">
-        <v>13247</v>
+        <v>13254</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -1706,7 +1832,7 @@
         <v>2519</v>
       </c>
       <c r="H57">
-        <v>13654</v>
+        <v>13658</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -1845,10 +1971,10 @@
         <v>1391</v>
       </c>
       <c r="G65">
-        <v>1795</v>
+        <v>1802</v>
       </c>
       <c r="H65">
-        <v>9701</v>
+        <v>9748</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -1868,10 +1994,10 @@
         <v>1364</v>
       </c>
       <c r="G66">
-        <v>1878</v>
+        <v>1891</v>
       </c>
       <c r="H66">
-        <v>10033</v>
+        <v>10080</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -1891,10 +2017,10 @@
         <v>1378</v>
       </c>
       <c r="G67">
-        <v>1845</v>
+        <v>1848</v>
       </c>
       <c r="H67">
-        <v>10102</v>
+        <v>10106</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -1917,7 +2043,7 @@
         <v>1494</v>
       </c>
       <c r="H68">
-        <v>9819</v>
+        <v>9822</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -1960,10 +2086,10 @@
         <v>1433</v>
       </c>
       <c r="G70">
-        <v>1726</v>
+        <v>1729</v>
       </c>
       <c r="H70">
-        <v>9963</v>
+        <v>9969</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -1986,7 +2112,7 @@
         <v>1804</v>
       </c>
       <c r="H71">
-        <v>10158</v>
+        <v>10161</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2125,10 +2251,10 @@
         <v>296</v>
       </c>
       <c r="G79">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="H79">
-        <v>2502</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2148,10 +2274,10 @@
         <v>368</v>
       </c>
       <c r="G80">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="H80">
-        <v>2663</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2174,7 +2300,7 @@
         <v>530</v>
       </c>
       <c r="H81">
-        <v>2711</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2243,7 +2369,7 @@
         <v>672</v>
       </c>
       <c r="H84">
-        <v>3284</v>
+        <v>3285</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -2266,7 +2392,7 @@
         <v>715</v>
       </c>
       <c r="H85">
-        <v>3496</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -2285,11 +2411,14 @@
       <c r="E86">
         <v>205</v>
       </c>
+      <c r="F86">
+        <v>258</v>
+      </c>
       <c r="G86">
-        <v>1041</v>
+        <v>1079</v>
       </c>
       <c r="H86">
-        <v>5194</v>
+        <v>5305</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -2308,11 +2437,14 @@
       <c r="E87">
         <v>622</v>
       </c>
+      <c r="F87">
+        <v>655</v>
+      </c>
       <c r="G87">
-        <v>1075</v>
+        <v>1117</v>
       </c>
       <c r="H87">
-        <v>5285</v>
+        <v>5424</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -2331,11 +2463,14 @@
       <c r="E88">
         <v>679</v>
       </c>
+      <c r="F88">
+        <v>669</v>
+      </c>
       <c r="G88">
-        <v>1078</v>
+        <v>1102</v>
       </c>
       <c r="H88">
-        <v>5377</v>
+        <v>5488</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -2354,11 +2489,14 @@
       <c r="E89">
         <v>645</v>
       </c>
+      <c r="F89">
+        <v>743</v>
+      </c>
       <c r="G89">
-        <v>1093</v>
+        <v>1111</v>
       </c>
       <c r="H89">
-        <v>5465</v>
+        <v>5535</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -2377,11 +2515,14 @@
       <c r="E90">
         <v>618</v>
       </c>
+      <c r="F90">
+        <v>749</v>
+      </c>
       <c r="G90">
-        <v>1040</v>
+        <v>1063</v>
       </c>
       <c r="H90">
-        <v>5570</v>
+        <v>5658</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -2400,11 +2541,14 @@
       <c r="E91">
         <v>708</v>
       </c>
+      <c r="F91">
+        <v>665</v>
+      </c>
       <c r="G91">
-        <v>1027</v>
+        <v>1054</v>
       </c>
       <c r="H91">
-        <v>5427</v>
+        <v>5506</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -2423,11 +2567,14 @@
       <c r="E92">
         <v>708</v>
       </c>
+      <c r="F92">
+        <v>673</v>
+      </c>
       <c r="G92">
-        <v>1053</v>
+        <v>1071</v>
       </c>
       <c r="H92">
-        <v>5436</v>
+        <v>5496</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -2446,11 +2593,14 @@
       <c r="E93">
         <v>704</v>
       </c>
+      <c r="F93">
+        <v>606</v>
+      </c>
       <c r="G93">
-        <v>1064</v>
+        <v>1082</v>
       </c>
       <c r="H93">
-        <v>5256</v>
+        <v>5302</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -2469,11 +2619,14 @@
       <c r="E94">
         <v>708</v>
       </c>
+      <c r="F94">
+        <v>738</v>
+      </c>
       <c r="G94">
-        <v>1095</v>
+        <v>1119</v>
       </c>
       <c r="H94">
-        <v>5406</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -2492,11 +2645,14 @@
       <c r="E95">
         <v>707</v>
       </c>
+      <c r="F95">
+        <v>645</v>
+      </c>
       <c r="G95">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="H95">
-        <v>5414</v>
+        <v>5419</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -2515,11 +2671,14 @@
       <c r="E96">
         <v>716</v>
       </c>
+      <c r="F96">
+        <v>654</v>
+      </c>
       <c r="G96">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H96">
-        <v>5423</v>
+        <v>5426</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -2538,6 +2697,9 @@
       <c r="E97">
         <v>643</v>
       </c>
+      <c r="F97">
+        <v>576</v>
+      </c>
       <c r="G97">
         <v>1085</v>
       </c>
@@ -2561,11 +2723,14 @@
       <c r="E98">
         <v>694</v>
       </c>
+      <c r="F98">
+        <v>657</v>
+      </c>
       <c r="G98">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="H98">
-        <v>5386</v>
+        <v>5389</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -2584,11 +2749,14 @@
       <c r="E99">
         <v>734</v>
       </c>
+      <c r="F99">
+        <v>657</v>
+      </c>
       <c r="G99">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H99">
-        <v>5346</v>
+        <v>5349</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -2607,11 +2775,14 @@
       <c r="E100">
         <v>11</v>
       </c>
+      <c r="F100">
+        <v>17</v>
+      </c>
       <c r="G100">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H100">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -2630,11 +2801,14 @@
       <c r="E101">
         <v>59</v>
       </c>
+      <c r="F101">
+        <v>46</v>
+      </c>
       <c r="G101">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H101">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -2653,11 +2827,14 @@
       <c r="E102">
         <v>60</v>
       </c>
+      <c r="F102">
+        <v>55</v>
+      </c>
       <c r="G102">
         <v>91</v>
       </c>
       <c r="H102">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -2676,11 +2853,14 @@
       <c r="E103">
         <v>60</v>
       </c>
+      <c r="F103">
+        <v>56</v>
+      </c>
       <c r="G103">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H103">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -2699,11 +2879,14 @@
       <c r="E104">
         <v>74</v>
       </c>
+      <c r="F104">
+        <v>49</v>
+      </c>
       <c r="G104">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H104">
-        <v>498</v>
+        <v>505</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -2722,11 +2905,14 @@
       <c r="E105">
         <v>64</v>
       </c>
+      <c r="F105">
+        <v>47</v>
+      </c>
       <c r="G105">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H105">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -2745,11 +2931,14 @@
       <c r="E106">
         <v>64</v>
       </c>
+      <c r="F106">
+        <v>66</v>
+      </c>
       <c r="G106">
         <v>102</v>
       </c>
       <c r="H106">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -2768,6 +2957,9 @@
       <c r="E107">
         <v>73</v>
       </c>
+      <c r="F107">
+        <v>62</v>
+      </c>
       <c r="G107">
         <v>111</v>
       </c>
@@ -2791,6 +2983,9 @@
       <c r="E108">
         <v>77</v>
       </c>
+      <c r="F108">
+        <v>70</v>
+      </c>
       <c r="G108">
         <v>160</v>
       </c>
@@ -2814,11 +3009,14 @@
       <c r="E109">
         <v>85</v>
       </c>
+      <c r="F109">
+        <v>57</v>
+      </c>
       <c r="G109">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H109">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -2837,11 +3035,14 @@
       <c r="E110">
         <v>69</v>
       </c>
+      <c r="F110">
+        <v>67</v>
+      </c>
       <c r="G110">
         <v>147</v>
       </c>
       <c r="H110">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -2860,6 +3061,9 @@
       <c r="E111">
         <v>69</v>
       </c>
+      <c r="F111">
+        <v>58</v>
+      </c>
       <c r="G111">
         <v>170</v>
       </c>
@@ -2883,11 +3087,14 @@
       <c r="E112">
         <v>84</v>
       </c>
+      <c r="F112">
+        <v>99</v>
+      </c>
       <c r="G112">
         <v>172</v>
       </c>
       <c r="H112">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -2906,6 +3113,9 @@
       <c r="E113">
         <v>105</v>
       </c>
+      <c r="F113">
+        <v>98</v>
+      </c>
       <c r="G113">
         <v>172</v>
       </c>
@@ -2929,11 +3139,14 @@
       <c r="E114">
         <v>7</v>
       </c>
+      <c r="F114">
+        <v>7</v>
+      </c>
       <c r="G114">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H114">
-        <v>116</v>
+        <v>129</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -2952,11 +3165,14 @@
       <c r="E115">
         <v>16</v>
       </c>
+      <c r="F115">
+        <v>22</v>
+      </c>
       <c r="G115">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H115">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -2975,11 +3191,14 @@
       <c r="E116">
         <v>14</v>
       </c>
+      <c r="F116">
+        <v>13</v>
+      </c>
       <c r="G116">
         <v>15</v>
       </c>
       <c r="H116">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -2998,11 +3217,14 @@
       <c r="E117">
         <v>15</v>
       </c>
+      <c r="F117">
+        <v>28</v>
+      </c>
       <c r="G117">
         <v>28</v>
       </c>
       <c r="H117">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -3021,11 +3243,14 @@
       <c r="E118">
         <v>21</v>
       </c>
+      <c r="F118">
+        <v>10</v>
+      </c>
       <c r="G118">
         <v>21</v>
       </c>
       <c r="H118">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -3044,11 +3269,14 @@
       <c r="E119">
         <v>16</v>
       </c>
+      <c r="F119">
+        <v>17</v>
+      </c>
       <c r="G119">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H119">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -3067,11 +3295,14 @@
       <c r="E120">
         <v>18</v>
       </c>
+      <c r="F120">
+        <v>12</v>
+      </c>
       <c r="G120">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H120">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -3090,11 +3321,14 @@
       <c r="E121">
         <v>17</v>
       </c>
+      <c r="F121">
+        <v>17</v>
+      </c>
       <c r="G121">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H121">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -3113,11 +3347,14 @@
       <c r="E122">
         <v>9</v>
       </c>
+      <c r="F122">
+        <v>12</v>
+      </c>
       <c r="G122">
         <v>53</v>
       </c>
       <c r="H122">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -3136,6 +3373,9 @@
       <c r="E123">
         <v>9</v>
       </c>
+      <c r="F123">
+        <v>17</v>
+      </c>
       <c r="G123">
         <v>50</v>
       </c>
@@ -3159,6 +3399,9 @@
       <c r="E124">
         <v>12</v>
       </c>
+      <c r="F124">
+        <v>23</v>
+      </c>
       <c r="G124">
         <v>46</v>
       </c>
@@ -3182,6 +3425,9 @@
       <c r="E125">
         <v>10</v>
       </c>
+      <c r="F125">
+        <v>22</v>
+      </c>
       <c r="G125">
         <v>47</v>
       </c>
@@ -3205,11 +3451,14 @@
       <c r="E126">
         <v>15</v>
       </c>
+      <c r="F126">
+        <v>21</v>
+      </c>
       <c r="G126">
         <v>54</v>
       </c>
       <c r="H126">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -3228,11 +3477,14 @@
       <c r="E127">
         <v>20</v>
       </c>
+      <c r="F127">
+        <v>21</v>
+      </c>
       <c r="G127">
         <v>50</v>
       </c>
       <c r="H127">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -3251,11 +3503,14 @@
       <c r="E128">
         <v>8</v>
       </c>
+      <c r="F128">
+        <v>11</v>
+      </c>
       <c r="G128">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H128">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -3274,11 +3529,14 @@
       <c r="E129">
         <v>32</v>
       </c>
+      <c r="F129">
+        <v>32</v>
+      </c>
       <c r="G129">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H129">
-        <v>317</v>
+        <v>324</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -3297,11 +3555,14 @@
       <c r="E130">
         <v>50</v>
       </c>
+      <c r="F130">
+        <v>41</v>
+      </c>
       <c r="G130">
         <v>64</v>
       </c>
       <c r="H130">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -3320,11 +3581,14 @@
       <c r="E131">
         <v>37</v>
       </c>
+      <c r="F131">
+        <v>45</v>
+      </c>
       <c r="G131">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H131">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -3343,11 +3607,14 @@
       <c r="E132">
         <v>46</v>
       </c>
+      <c r="F132">
+        <v>42</v>
+      </c>
       <c r="G132">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H132">
-        <v>393</v>
+        <v>406</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -3366,11 +3633,14 @@
       <c r="E133">
         <v>38</v>
       </c>
+      <c r="F133">
+        <v>69</v>
+      </c>
       <c r="G133">
         <v>107</v>
       </c>
       <c r="H133">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -3389,11 +3659,14 @@
       <c r="E134">
         <v>41</v>
       </c>
+      <c r="F134">
+        <v>53</v>
+      </c>
       <c r="G134">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H134">
-        <v>476</v>
+        <v>483</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -3412,11 +3685,14 @@
       <c r="E135">
         <v>51</v>
       </c>
+      <c r="F135">
+        <v>56</v>
+      </c>
       <c r="G135">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H135">
-        <v>541</v>
+        <v>548</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -3435,11 +3711,14 @@
       <c r="E136">
         <v>46</v>
       </c>
+      <c r="F136">
+        <v>76</v>
+      </c>
       <c r="G136">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H136">
-        <v>621</v>
+        <v>628</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -3458,11 +3737,14 @@
       <c r="E137">
         <v>47</v>
       </c>
+      <c r="F137">
+        <v>86</v>
+      </c>
       <c r="G137">
         <v>169</v>
       </c>
       <c r="H137">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -3481,6 +3763,9 @@
       <c r="E138">
         <v>51</v>
       </c>
+      <c r="F138">
+        <v>74</v>
+      </c>
       <c r="G138">
         <v>190</v>
       </c>
@@ -3504,6 +3789,9 @@
       <c r="E139">
         <v>69</v>
       </c>
+      <c r="F139">
+        <v>86</v>
+      </c>
       <c r="G139">
         <v>218</v>
       </c>
@@ -3527,11 +3815,14 @@
       <c r="E140">
         <v>78</v>
       </c>
+      <c r="F140">
+        <v>95</v>
+      </c>
       <c r="G140">
         <v>162</v>
       </c>
       <c r="H140">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -3550,6 +3841,9 @@
       <c r="E141">
         <v>88</v>
       </c>
+      <c r="F141">
+        <v>89</v>
+      </c>
       <c r="G141">
         <v>195</v>
       </c>
@@ -3573,6 +3867,9 @@
       <c r="E142">
         <v>0</v>
       </c>
+      <c r="F142">
+        <v>0</v>
+      </c>
       <c r="G142">
         <v>1</v>
       </c>
@@ -3596,6 +3893,9 @@
       <c r="E143">
         <v>0</v>
       </c>
+      <c r="F143">
+        <v>1</v>
+      </c>
       <c r="G143">
         <v>4</v>
       </c>
@@ -3619,6 +3919,9 @@
       <c r="E144">
         <v>0</v>
       </c>
+      <c r="F144">
+        <v>1</v>
+      </c>
       <c r="G144">
         <v>1</v>
       </c>
@@ -3642,6 +3945,9 @@
       <c r="E145">
         <v>0</v>
       </c>
+      <c r="F145">
+        <v>1</v>
+      </c>
       <c r="G145">
         <v>1</v>
       </c>
@@ -3665,11 +3971,14 @@
       <c r="E146">
         <v>2</v>
       </c>
+      <c r="F146">
+        <v>1</v>
+      </c>
       <c r="G146">
         <v>2</v>
       </c>
       <c r="H146">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -3688,6 +3997,9 @@
       <c r="E147">
         <v>2</v>
       </c>
+      <c r="F147">
+        <v>0</v>
+      </c>
       <c r="G147">
         <v>4</v>
       </c>
@@ -3711,6 +4023,9 @@
       <c r="E148">
         <v>1</v>
       </c>
+      <c r="F148">
+        <v>1</v>
+      </c>
       <c r="G148">
         <v>1</v>
       </c>
@@ -3734,6 +4049,9 @@
       <c r="E149">
         <v>0</v>
       </c>
+      <c r="F149">
+        <v>2</v>
+      </c>
       <c r="G149">
         <v>0</v>
       </c>
@@ -3757,6 +4075,9 @@
       <c r="E150">
         <v>2</v>
       </c>
+      <c r="F150">
+        <v>1</v>
+      </c>
       <c r="G150">
         <v>2</v>
       </c>
@@ -3780,6 +4101,9 @@
       <c r="E151">
         <v>1</v>
       </c>
+      <c r="F151">
+        <v>1</v>
+      </c>
       <c r="G151">
         <v>1</v>
       </c>
@@ -3803,6 +4127,9 @@
       <c r="E152">
         <v>0</v>
       </c>
+      <c r="F152">
+        <v>0</v>
+      </c>
       <c r="G152">
         <v>0</v>
       </c>
@@ -3826,6 +4153,9 @@
       <c r="E153">
         <v>0</v>
       </c>
+      <c r="F153">
+        <v>1</v>
+      </c>
       <c r="G153">
         <v>0</v>
       </c>
@@ -3849,6 +4179,9 @@
       <c r="E154">
         <v>1</v>
       </c>
+      <c r="F154">
+        <v>1</v>
+      </c>
       <c r="G154">
         <v>1</v>
       </c>
@@ -3872,6 +4205,9 @@
       <c r="E155">
         <v>0</v>
       </c>
+      <c r="F155">
+        <v>0</v>
+      </c>
       <c r="G155">
         <v>0</v>
       </c>
@@ -3895,6 +4231,9 @@
       <c r="E156">
         <v>1</v>
       </c>
+      <c r="F156">
+        <v>3</v>
+      </c>
       <c r="G156">
         <v>27</v>
       </c>
@@ -3915,6 +4254,9 @@
       <c r="E157">
         <v>7</v>
       </c>
+      <c r="F157">
+        <v>5</v>
+      </c>
       <c r="G157">
         <v>27</v>
       </c>
@@ -3935,8 +4277,11 @@
       <c r="E158">
         <v>9</v>
       </c>
+      <c r="F158">
+        <v>14</v>
+      </c>
       <c r="G158">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -3955,8 +4300,11 @@
       <c r="E159">
         <v>10</v>
       </c>
+      <c r="F159">
+        <v>33</v>
+      </c>
       <c r="G159">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -3975,8 +4323,11 @@
       <c r="E160">
         <v>14</v>
       </c>
+      <c r="F160">
+        <v>19</v>
+      </c>
       <c r="G160">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -3995,8 +4346,11 @@
       <c r="E161">
         <v>10</v>
       </c>
+      <c r="F161">
+        <v>17</v>
+      </c>
       <c r="G161">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -4015,8 +4369,11 @@
       <c r="E162">
         <v>15</v>
       </c>
+      <c r="F162">
+        <v>26</v>
+      </c>
       <c r="G162">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -4035,11 +4392,14 @@
       <c r="E163">
         <v>13</v>
       </c>
+      <c r="F163">
+        <v>32</v>
+      </c>
       <c r="G163">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H163">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -4058,11 +4418,14 @@
       <c r="E164">
         <v>27</v>
       </c>
+      <c r="F164">
+        <v>35</v>
+      </c>
       <c r="G164">
         <v>63</v>
       </c>
       <c r="H164">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -4081,6 +4444,9 @@
       <c r="E165">
         <v>22</v>
       </c>
+      <c r="F165">
+        <v>28</v>
+      </c>
       <c r="G165">
         <v>67</v>
       </c>
@@ -4104,11 +4470,14 @@
       <c r="E166">
         <v>24</v>
       </c>
+      <c r="F166">
+        <v>39</v>
+      </c>
       <c r="G166">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H166">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -4127,6 +4496,9 @@
       <c r="E167">
         <v>23</v>
       </c>
+      <c r="F167">
+        <v>37</v>
+      </c>
       <c r="G167">
         <v>59</v>
       </c>
@@ -4150,6 +4522,9 @@
       <c r="E168">
         <v>39</v>
       </c>
+      <c r="F168">
+        <v>31</v>
+      </c>
       <c r="G168">
         <v>73</v>
       </c>
@@ -4173,6 +4548,9 @@
       <c r="E169">
         <v>31</v>
       </c>
+      <c r="F169">
+        <v>45</v>
+      </c>
       <c r="G169">
         <v>83</v>
       </c>
@@ -4196,8 +4574,11 @@
       <c r="E170">
         <v>90</v>
       </c>
+      <c r="F170">
+        <v>97</v>
+      </c>
       <c r="G170">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -4216,8 +4597,11 @@
       <c r="E171">
         <v>99</v>
       </c>
+      <c r="F171">
+        <v>73</v>
+      </c>
       <c r="G171">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -4236,8 +4620,11 @@
       <c r="E172">
         <v>95</v>
       </c>
+      <c r="F172">
+        <v>74</v>
+      </c>
       <c r="G172">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -4256,8 +4643,11 @@
       <c r="E173">
         <v>99</v>
       </c>
+      <c r="F173">
+        <v>64</v>
+      </c>
       <c r="G173">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -4276,8 +4666,11 @@
       <c r="E174">
         <v>80</v>
       </c>
+      <c r="F174">
+        <v>60</v>
+      </c>
       <c r="G174">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -4296,8 +4689,11 @@
       <c r="E175">
         <v>91</v>
       </c>
+      <c r="F175">
+        <v>63</v>
+      </c>
       <c r="G175">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -4316,8 +4712,11 @@
       <c r="E176">
         <v>82</v>
       </c>
+      <c r="F176">
+        <v>48</v>
+      </c>
       <c r="G176">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -4336,11 +4735,14 @@
       <c r="E177">
         <v>65</v>
       </c>
+      <c r="F177">
+        <v>35</v>
+      </c>
       <c r="G177">
         <v>64</v>
       </c>
       <c r="H177">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -4359,6 +4761,9 @@
       <c r="E178">
         <v>64</v>
       </c>
+      <c r="F178">
+        <v>46</v>
+      </c>
       <c r="G178">
         <v>64</v>
       </c>
@@ -4382,6 +4787,9 @@
       <c r="E179">
         <v>79</v>
       </c>
+      <c r="F179">
+        <v>35</v>
+      </c>
       <c r="G179">
         <v>36</v>
       </c>
@@ -4405,6 +4813,9 @@
       <c r="E180">
         <v>63</v>
       </c>
+      <c r="F180">
+        <v>35</v>
+      </c>
       <c r="G180">
         <v>58</v>
       </c>
@@ -4428,6 +4839,9 @@
       <c r="E181">
         <v>51</v>
       </c>
+      <c r="F181">
+        <v>28</v>
+      </c>
       <c r="G181">
         <v>79</v>
       </c>
@@ -4451,6 +4865,9 @@
       <c r="E182">
         <v>58</v>
       </c>
+      <c r="F182">
+        <v>31</v>
+      </c>
       <c r="G182">
         <v>65</v>
       </c>
@@ -4474,11 +4891,14 @@
       <c r="E183">
         <v>53</v>
       </c>
+      <c r="F183">
+        <v>39</v>
+      </c>
       <c r="G183">
         <v>40</v>
       </c>
       <c r="H183">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -4497,11 +4917,14 @@
       <c r="E184">
         <v>678</v>
       </c>
+      <c r="F184">
+        <v>486</v>
+      </c>
       <c r="G184">
-        <v>995</v>
+        <v>1015</v>
       </c>
       <c r="H184">
-        <v>5316</v>
+        <v>5382</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -4520,11 +4943,14 @@
       <c r="E185">
         <v>662</v>
       </c>
+      <c r="F185">
+        <v>471</v>
+      </c>
       <c r="G185">
-        <v>1073</v>
+        <v>1109</v>
       </c>
       <c r="H185">
-        <v>5428</v>
+        <v>5535</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -4543,11 +4969,14 @@
       <c r="E186">
         <v>707</v>
       </c>
+      <c r="F186">
+        <v>569</v>
+      </c>
       <c r="G186">
-        <v>1107</v>
+        <v>1133</v>
       </c>
       <c r="H186">
-        <v>5545</v>
+        <v>5616</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -4566,11 +4995,14 @@
       <c r="E187">
         <v>711</v>
       </c>
+      <c r="F187">
+        <v>503</v>
+      </c>
       <c r="G187">
-        <v>1027</v>
+        <v>1043</v>
       </c>
       <c r="H187">
-        <v>5641</v>
+        <v>5703</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -4589,11 +5021,14 @@
       <c r="E188">
         <v>751</v>
       </c>
+      <c r="F188">
+        <v>481</v>
+      </c>
       <c r="G188">
-        <v>1082</v>
+        <v>1104</v>
       </c>
       <c r="H188">
-        <v>5754</v>
+        <v>5821</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -4612,11 +5047,14 @@
       <c r="E189">
         <v>739</v>
       </c>
+      <c r="F189">
+        <v>551</v>
+      </c>
       <c r="G189">
-        <v>1178</v>
+        <v>1202</v>
       </c>
       <c r="H189">
-        <v>5856</v>
+        <v>5944</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -4635,11 +5073,14 @@
       <c r="E190">
         <v>723</v>
       </c>
+      <c r="F190">
+        <v>493</v>
+      </c>
       <c r="G190">
-        <v>1144</v>
+        <v>1152</v>
       </c>
       <c r="H190">
-        <v>5992</v>
+        <v>6055</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -4658,11 +5099,14 @@
       <c r="E191">
         <v>764</v>
       </c>
+      <c r="F191">
+        <v>542</v>
+      </c>
       <c r="G191">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H191">
-        <v>5909</v>
+        <v>5930</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -4681,11 +5125,14 @@
       <c r="E192">
         <v>797</v>
       </c>
+      <c r="F192">
+        <v>606</v>
+      </c>
       <c r="G192">
-        <v>1162</v>
+        <v>1170</v>
       </c>
       <c r="H192">
-        <v>6128</v>
+        <v>6146</v>
       </c>
     </row>
     <row r="193" spans="1:8">
@@ -4704,11 +5151,14 @@
       <c r="E193">
         <v>770</v>
       </c>
+      <c r="F193">
+        <v>504</v>
+      </c>
       <c r="G193">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="H193">
-        <v>6200</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -4727,11 +5177,14 @@
       <c r="E194">
         <v>710</v>
       </c>
+      <c r="F194">
+        <v>582</v>
+      </c>
       <c r="G194">
         <v>713</v>
       </c>
       <c r="H194">
-        <v>5763</v>
+        <v>5765</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -4750,6 +5203,9 @@
       <c r="E195">
         <v>760</v>
       </c>
+      <c r="F195">
+        <v>574</v>
+      </c>
       <c r="G195">
         <v>1212</v>
       </c>
@@ -4773,11 +5229,14 @@
       <c r="E196">
         <v>841</v>
       </c>
+      <c r="F196">
+        <v>494</v>
+      </c>
       <c r="G196">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H196">
-        <v>6282</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="197" spans="1:8">
@@ -4796,11 +5255,14 @@
       <c r="E197">
         <v>842</v>
       </c>
+      <c r="F197">
+        <v>529</v>
+      </c>
       <c r="G197">
         <v>1356</v>
       </c>
       <c r="H197">
-        <v>6550</v>
+        <v>6551</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -4819,11 +5281,14 @@
       <c r="E198">
         <v>170</v>
       </c>
+      <c r="F198">
+        <v>209</v>
+      </c>
       <c r="G198">
-        <v>847</v>
+        <v>876</v>
       </c>
       <c r="H198">
-        <v>4255</v>
+        <v>4344</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -4842,11 +5307,14 @@
       <c r="E199">
         <v>522</v>
       </c>
+      <c r="F199">
+        <v>526</v>
+      </c>
       <c r="G199">
-        <v>877</v>
+        <v>910</v>
       </c>
       <c r="H199">
-        <v>4359</v>
+        <v>4477</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -4865,11 +5333,14 @@
       <c r="E200">
         <v>569</v>
       </c>
+      <c r="F200">
+        <v>515</v>
+      </c>
       <c r="G200">
-        <v>895</v>
+        <v>911</v>
       </c>
       <c r="H200">
-        <v>4446</v>
+        <v>4529</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -4888,11 +5359,14 @@
       <c r="E201">
         <v>524</v>
       </c>
+      <c r="F201">
+        <v>604</v>
+      </c>
       <c r="G201">
-        <v>902</v>
+        <v>917</v>
       </c>
       <c r="H201">
-        <v>4544</v>
+        <v>4598</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -4911,11 +5385,14 @@
       <c r="E202">
         <v>522</v>
       </c>
+      <c r="F202">
+        <v>609</v>
+      </c>
       <c r="G202">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="H202">
-        <v>4628</v>
+        <v>4698</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -4934,11 +5411,14 @@
       <c r="E203">
         <v>586</v>
       </c>
+      <c r="F203">
+        <v>543</v>
+      </c>
       <c r="G203">
-        <v>825</v>
+        <v>843</v>
       </c>
       <c r="H203">
-        <v>4490</v>
+        <v>4551</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -4957,11 +5437,14 @@
       <c r="E204">
         <v>585</v>
       </c>
+      <c r="F204">
+        <v>542</v>
+      </c>
       <c r="G204">
-        <v>854</v>
+        <v>868</v>
       </c>
       <c r="H204">
-        <v>4470</v>
+        <v>4515</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -4980,11 +5463,14 @@
       <c r="E205">
         <v>598</v>
       </c>
+      <c r="F205">
+        <v>475</v>
+      </c>
       <c r="G205">
-        <v>847</v>
+        <v>863</v>
       </c>
       <c r="H205">
-        <v>4305</v>
+        <v>4346</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -5003,11 +5489,14 @@
       <c r="E206">
         <v>557</v>
       </c>
+      <c r="F206">
+        <v>599</v>
+      </c>
       <c r="G206">
-        <v>876</v>
+        <v>897</v>
       </c>
       <c r="H206">
-        <v>4395</v>
+        <v>4441</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -5026,11 +5515,14 @@
       <c r="E207">
         <v>595</v>
       </c>
+      <c r="F207">
+        <v>525</v>
+      </c>
       <c r="G207">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="H207">
-        <v>4363</v>
+        <v>4368</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -5049,11 +5541,14 @@
       <c r="E208">
         <v>593</v>
       </c>
+      <c r="F208">
+        <v>523</v>
+      </c>
       <c r="G208">
         <v>854</v>
       </c>
       <c r="H208">
-        <v>4315</v>
+        <v>4316</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -5072,6 +5567,9 @@
       <c r="E209">
         <v>539</v>
       </c>
+      <c r="F209">
+        <v>449</v>
+      </c>
       <c r="G209">
         <v>775</v>
       </c>
@@ -5095,11 +5593,14 @@
       <c r="E210">
         <v>553</v>
       </c>
+      <c r="F210">
+        <v>507</v>
+      </c>
       <c r="G210">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="H210">
-        <v>4105</v>
+        <v>4107</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -5118,11 +5619,14 @@
       <c r="E211">
         <v>570</v>
       </c>
+      <c r="F211">
+        <v>495</v>
+      </c>
       <c r="G211">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H211">
-        <v>4018</v>
+        <v>4021</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -5141,11 +5645,14 @@
       <c r="E212">
         <v>9</v>
       </c>
+      <c r="F212">
+        <v>13</v>
+      </c>
       <c r="G212">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H212">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -5164,11 +5671,14 @@
       <c r="E213">
         <v>43</v>
       </c>
+      <c r="F213">
+        <v>35</v>
+      </c>
       <c r="G213">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H213">
-        <v>354</v>
+        <v>361</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -5187,6 +5697,9 @@
       <c r="E214">
         <v>40</v>
       </c>
+      <c r="F214">
+        <v>41</v>
+      </c>
       <c r="G214">
         <v>66</v>
       </c>
@@ -5210,11 +5723,14 @@
       <c r="E215">
         <v>49</v>
       </c>
+      <c r="F215">
+        <v>49</v>
+      </c>
       <c r="G215">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H215">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -5233,11 +5749,14 @@
       <c r="E216">
         <v>55</v>
       </c>
+      <c r="F216">
+        <v>37</v>
+      </c>
       <c r="G216">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H216">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -5256,11 +5775,14 @@
       <c r="E217">
         <v>48</v>
       </c>
+      <c r="F217">
+        <v>35</v>
+      </c>
       <c r="G217">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H217">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -5279,11 +5801,14 @@
       <c r="E218">
         <v>48</v>
       </c>
+      <c r="F218">
+        <v>51</v>
+      </c>
       <c r="G218">
         <v>68</v>
       </c>
       <c r="H218">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -5302,6 +5827,9 @@
       <c r="E219">
         <v>57</v>
       </c>
+      <c r="F219">
+        <v>45</v>
+      </c>
       <c r="G219">
         <v>84</v>
       </c>
@@ -5325,6 +5853,9 @@
       <c r="E220">
         <v>61</v>
       </c>
+      <c r="F220">
+        <v>48</v>
+      </c>
       <c r="G220">
         <v>117</v>
       </c>
@@ -5348,11 +5879,14 @@
       <c r="E221">
         <v>61</v>
       </c>
+      <c r="F221">
+        <v>45</v>
+      </c>
       <c r="G221">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H221">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="222" spans="1:8">
@@ -5371,11 +5905,14 @@
       <c r="E222">
         <v>47</v>
       </c>
+      <c r="F222">
+        <v>50</v>
+      </c>
       <c r="G222">
         <v>96</v>
       </c>
       <c r="H222">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="223" spans="1:8">
@@ -5394,6 +5931,9 @@
       <c r="E223">
         <v>57</v>
       </c>
+      <c r="F223">
+        <v>44</v>
+      </c>
       <c r="G223">
         <v>114</v>
       </c>
@@ -5417,11 +5957,14 @@
       <c r="E224">
         <v>68</v>
       </c>
+      <c r="F224">
+        <v>70</v>
+      </c>
       <c r="G224">
         <v>117</v>
       </c>
       <c r="H224">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="225" spans="1:8">
@@ -5440,6 +5983,9 @@
       <c r="E225">
         <v>72</v>
       </c>
+      <c r="F225">
+        <v>74</v>
+      </c>
       <c r="G225">
         <v>125</v>
       </c>
@@ -5463,11 +6009,14 @@
       <c r="E226">
         <v>6</v>
       </c>
+      <c r="F226">
+        <v>5</v>
+      </c>
       <c r="G226">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H226">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -5486,11 +6035,14 @@
       <c r="E227">
         <v>12</v>
       </c>
+      <c r="F227">
+        <v>19</v>
+      </c>
       <c r="G227">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H227">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="228" spans="1:8">
@@ -5509,11 +6061,14 @@
       <c r="E228">
         <v>12</v>
       </c>
+      <c r="F228">
+        <v>11</v>
+      </c>
       <c r="G228">
         <v>13</v>
       </c>
       <c r="H228">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="229" spans="1:8">
@@ -5532,11 +6087,14 @@
       <c r="E229">
         <v>11</v>
       </c>
+      <c r="F229">
+        <v>22</v>
+      </c>
       <c r="G229">
         <v>24</v>
       </c>
       <c r="H229">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="230" spans="1:8">
@@ -5555,11 +6113,14 @@
       <c r="E230">
         <v>19</v>
       </c>
+      <c r="F230">
+        <v>9</v>
+      </c>
       <c r="G230">
         <v>16</v>
       </c>
       <c r="H230">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="231" spans="1:8">
@@ -5578,11 +6139,14 @@
       <c r="E231">
         <v>12</v>
       </c>
+      <c r="F231">
+        <v>14</v>
+      </c>
       <c r="G231">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H231">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="232" spans="1:8">
@@ -5601,11 +6165,14 @@
       <c r="E232">
         <v>13</v>
       </c>
+      <c r="F232">
+        <v>11</v>
+      </c>
       <c r="G232">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H232">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="233" spans="1:8">
@@ -5624,11 +6191,14 @@
       <c r="E233">
         <v>14</v>
       </c>
+      <c r="F233">
+        <v>12</v>
+      </c>
       <c r="G233">
         <v>34</v>
       </c>
       <c r="H233">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="234" spans="1:8">
@@ -5647,11 +6217,14 @@
       <c r="E234">
         <v>6</v>
       </c>
+      <c r="F234">
+        <v>10</v>
+      </c>
       <c r="G234">
         <v>46</v>
       </c>
       <c r="H234">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -5670,6 +6243,9 @@
       <c r="E235">
         <v>8</v>
       </c>
+      <c r="F235">
+        <v>14</v>
+      </c>
       <c r="G235">
         <v>43</v>
       </c>
@@ -5693,6 +6269,9 @@
       <c r="E236">
         <v>10</v>
       </c>
+      <c r="F236">
+        <v>17</v>
+      </c>
       <c r="G236">
         <v>32</v>
       </c>
@@ -5716,6 +6295,9 @@
       <c r="E237">
         <v>6</v>
       </c>
+      <c r="F237">
+        <v>19</v>
+      </c>
       <c r="G237">
         <v>32</v>
       </c>
@@ -5739,11 +6321,14 @@
       <c r="E238">
         <v>10</v>
       </c>
+      <c r="F238">
+        <v>16</v>
+      </c>
       <c r="G238">
         <v>40</v>
       </c>
       <c r="H238">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -5762,11 +6347,14 @@
       <c r="E239">
         <v>16</v>
       </c>
+      <c r="F239">
+        <v>17</v>
+      </c>
       <c r="G239">
         <v>37</v>
       </c>
       <c r="H239">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -5785,11 +6373,14 @@
       <c r="E240">
         <v>5</v>
       </c>
+      <c r="F240">
+        <v>7</v>
+      </c>
       <c r="G240">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H240">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -5808,11 +6399,14 @@
       <c r="E241">
         <v>26</v>
       </c>
+      <c r="F241">
+        <v>29</v>
+      </c>
       <c r="G241">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H241">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -5831,11 +6425,14 @@
       <c r="E242">
         <v>45</v>
       </c>
+      <c r="F242">
+        <v>34</v>
+      </c>
       <c r="G242">
         <v>53</v>
       </c>
       <c r="H242">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -5854,11 +6451,14 @@
       <c r="E243">
         <v>30</v>
       </c>
+      <c r="F243">
+        <v>40</v>
+      </c>
       <c r="G243">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H243">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="244" spans="1:8">
@@ -5877,11 +6477,14 @@
       <c r="E244">
         <v>40</v>
       </c>
+      <c r="F244">
+        <v>37</v>
+      </c>
       <c r="G244">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H244">
-        <v>326</v>
+        <v>338</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -5900,11 +6503,14 @@
       <c r="E245">
         <v>28</v>
       </c>
+      <c r="F245">
+        <v>59</v>
+      </c>
       <c r="G245">
         <v>94</v>
       </c>
       <c r="H245">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -5923,11 +6529,14 @@
       <c r="E246">
         <v>36</v>
       </c>
+      <c r="F246">
+        <v>45</v>
+      </c>
       <c r="G246">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H246">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="247" spans="1:8">
@@ -5946,11 +6555,14 @@
       <c r="E247">
         <v>44</v>
       </c>
+      <c r="F247">
+        <v>45</v>
+      </c>
       <c r="G247">
         <v>107</v>
       </c>
       <c r="H247">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -5969,11 +6581,14 @@
       <c r="E248">
         <v>39</v>
       </c>
+      <c r="F248">
+        <v>63</v>
+      </c>
       <c r="G248">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H248">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="249" spans="1:8">
@@ -5992,11 +6607,14 @@
       <c r="E249">
         <v>37</v>
       </c>
+      <c r="F249">
+        <v>70</v>
+      </c>
       <c r="G249">
         <v>138</v>
       </c>
       <c r="H249">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="250" spans="1:8">
@@ -6015,6 +6633,9 @@
       <c r="E250">
         <v>37</v>
       </c>
+      <c r="F250">
+        <v>54</v>
+      </c>
       <c r="G250">
         <v>143</v>
       </c>
@@ -6038,6 +6659,9 @@
       <c r="E251">
         <v>58</v>
       </c>
+      <c r="F251">
+        <v>67</v>
+      </c>
       <c r="G251">
         <v>145</v>
       </c>
@@ -6061,11 +6685,14 @@
       <c r="E252">
         <v>63</v>
       </c>
+      <c r="F252">
+        <v>73</v>
+      </c>
       <c r="G252">
         <v>119</v>
       </c>
       <c r="H252">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="253" spans="1:8">
@@ -6084,6 +6711,9 @@
       <c r="E253">
         <v>73</v>
       </c>
+      <c r="F253">
+        <v>68</v>
+      </c>
       <c r="G253">
         <v>143</v>
       </c>
@@ -6107,6 +6737,9 @@
       <c r="E254">
         <v>0</v>
       </c>
+      <c r="F254">
+        <v>0</v>
+      </c>
       <c r="G254">
         <v>1</v>
       </c>
@@ -6130,6 +6763,9 @@
       <c r="E255">
         <v>0</v>
       </c>
+      <c r="F255">
+        <v>0</v>
+      </c>
       <c r="G255">
         <v>3</v>
       </c>
@@ -6153,6 +6789,9 @@
       <c r="E256">
         <v>0</v>
       </c>
+      <c r="F256">
+        <v>0</v>
+      </c>
       <c r="G256">
         <v>1</v>
       </c>
@@ -6176,6 +6815,9 @@
       <c r="E257">
         <v>0</v>
       </c>
+      <c r="F257">
+        <v>1</v>
+      </c>
       <c r="G257">
         <v>1</v>
       </c>
@@ -6199,6 +6841,9 @@
       <c r="E258">
         <v>0</v>
       </c>
+      <c r="F258">
+        <v>1</v>
+      </c>
       <c r="G258">
         <v>2</v>
       </c>
@@ -6222,6 +6867,9 @@
       <c r="E259">
         <v>2</v>
       </c>
+      <c r="F259">
+        <v>0</v>
+      </c>
       <c r="G259">
         <v>2</v>
       </c>
@@ -6245,6 +6893,9 @@
       <c r="E260">
         <v>1</v>
       </c>
+      <c r="F260">
+        <v>1</v>
+      </c>
       <c r="G260">
         <v>1</v>
       </c>
@@ -6268,6 +6919,9 @@
       <c r="E261">
         <v>0</v>
       </c>
+      <c r="F261">
+        <v>0</v>
+      </c>
       <c r="G261">
         <v>0</v>
       </c>
@@ -6291,6 +6945,9 @@
       <c r="E262">
         <v>1</v>
       </c>
+      <c r="F262">
+        <v>1</v>
+      </c>
       <c r="G262">
         <v>2</v>
       </c>
@@ -6314,6 +6971,9 @@
       <c r="E263">
         <v>1</v>
       </c>
+      <c r="F263">
+        <v>1</v>
+      </c>
       <c r="G263">
         <v>0</v>
       </c>
@@ -6337,6 +6997,9 @@
       <c r="E264">
         <v>0</v>
       </c>
+      <c r="F264">
+        <v>0</v>
+      </c>
       <c r="G264">
         <v>0</v>
       </c>
@@ -6360,6 +7023,9 @@
       <c r="E265">
         <v>0</v>
       </c>
+      <c r="F265">
+        <v>0</v>
+      </c>
       <c r="G265">
         <v>0</v>
       </c>
@@ -6383,6 +7049,9 @@
       <c r="E266">
         <v>1</v>
       </c>
+      <c r="F266">
+        <v>1</v>
+      </c>
       <c r="G266">
         <v>1</v>
       </c>
@@ -6406,6 +7075,9 @@
       <c r="E267">
         <v>0</v>
       </c>
+      <c r="F267">
+        <v>0</v>
+      </c>
       <c r="G267">
         <v>0</v>
       </c>
@@ -6429,6 +7101,9 @@
       <c r="E268">
         <v>1</v>
       </c>
+      <c r="F268">
+        <v>1</v>
+      </c>
       <c r="G268">
         <v>19</v>
       </c>
@@ -6452,6 +7127,9 @@
       <c r="E269">
         <v>6</v>
       </c>
+      <c r="F269">
+        <v>4</v>
+      </c>
       <c r="G269">
         <v>18</v>
       </c>
@@ -6475,11 +7153,14 @@
       <c r="E270">
         <v>7</v>
       </c>
+      <c r="F270">
+        <v>11</v>
+      </c>
       <c r="G270">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H270">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -6498,11 +7179,14 @@
       <c r="E271">
         <v>8</v>
       </c>
+      <c r="F271">
+        <v>27</v>
+      </c>
       <c r="G271">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H271">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -6521,11 +7205,14 @@
       <c r="E272">
         <v>12</v>
       </c>
+      <c r="F272">
+        <v>11</v>
+      </c>
       <c r="G272">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H272">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -6544,11 +7231,14 @@
       <c r="E273">
         <v>9</v>
       </c>
+      <c r="F273">
+        <v>12</v>
+      </c>
       <c r="G273">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H273">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -6567,11 +7257,14 @@
       <c r="E274">
         <v>8</v>
       </c>
+      <c r="F274">
+        <v>19</v>
+      </c>
       <c r="G274">
         <v>32</v>
       </c>
       <c r="H274">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -6590,11 +7283,14 @@
       <c r="E275">
         <v>8</v>
       </c>
+      <c r="F275">
+        <v>26</v>
+      </c>
       <c r="G275">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H275">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -6613,11 +7309,14 @@
       <c r="E276">
         <v>22</v>
       </c>
+      <c r="F276">
+        <v>24</v>
+      </c>
       <c r="G276">
         <v>45</v>
       </c>
       <c r="H276">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -6636,6 +7335,9 @@
       <c r="E277">
         <v>16</v>
       </c>
+      <c r="F277">
+        <v>21</v>
+      </c>
       <c r="G277">
         <v>52</v>
       </c>
@@ -6659,11 +7361,14 @@
       <c r="E278">
         <v>21</v>
       </c>
+      <c r="F278">
+        <v>28</v>
+      </c>
       <c r="G278">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H278">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="279" spans="1:8">
@@ -6682,6 +7387,9 @@
       <c r="E279">
         <v>18</v>
       </c>
+      <c r="F279">
+        <v>27</v>
+      </c>
       <c r="G279">
         <v>40</v>
       </c>
@@ -6705,6 +7413,9 @@
       <c r="E280">
         <v>29</v>
       </c>
+      <c r="F280">
+        <v>24</v>
+      </c>
       <c r="G280">
         <v>45</v>
       </c>
@@ -6728,6 +7439,9 @@
       <c r="E281">
         <v>25</v>
       </c>
+      <c r="F281">
+        <v>29</v>
+      </c>
       <c r="G281">
         <v>61</v>
       </c>
@@ -6751,11 +7465,14 @@
       <c r="E282">
         <v>73</v>
       </c>
+      <c r="F282">
+        <v>82</v>
+      </c>
       <c r="G282">
         <v>80</v>
       </c>
       <c r="H282">
-        <v>468</v>
+        <v>475</v>
       </c>
     </row>
     <row r="283" spans="1:8">
@@ -6774,11 +7491,14 @@
       <c r="E283">
         <v>82</v>
       </c>
+      <c r="F283">
+        <v>54</v>
+      </c>
       <c r="G283">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H283">
-        <v>444</v>
+        <v>456</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -6797,11 +7517,14 @@
       <c r="E284">
         <v>74</v>
       </c>
+      <c r="F284">
+        <v>63</v>
+      </c>
       <c r="G284">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H284">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="285" spans="1:8">
@@ -6820,11 +7543,14 @@
       <c r="E285">
         <v>80</v>
       </c>
+      <c r="F285">
+        <v>51</v>
+      </c>
       <c r="G285">
         <v>64</v>
       </c>
       <c r="H285">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="286" spans="1:8">
@@ -6843,11 +7569,14 @@
       <c r="E286">
         <v>62</v>
       </c>
+      <c r="F286">
+        <v>47</v>
+      </c>
       <c r="G286">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H286">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="287" spans="1:8">
@@ -6866,11 +7595,14 @@
       <c r="E287">
         <v>70</v>
       </c>
+      <c r="F287">
+        <v>57</v>
+      </c>
       <c r="G287">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H287">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -6889,11 +7621,14 @@
       <c r="E288">
         <v>67</v>
       </c>
+      <c r="F288">
+        <v>38</v>
+      </c>
       <c r="G288">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H288">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="289" spans="1:8">
@@ -6912,6 +7647,9 @@
       <c r="E289">
         <v>51</v>
       </c>
+      <c r="F289">
+        <v>29</v>
+      </c>
       <c r="G289">
         <v>49</v>
       </c>
@@ -6935,6 +7673,9 @@
       <c r="E290">
         <v>54</v>
       </c>
+      <c r="F290">
+        <v>34</v>
+      </c>
       <c r="G290">
         <v>53</v>
       </c>
@@ -6958,6 +7699,9 @@
       <c r="E291">
         <v>66</v>
       </c>
+      <c r="F291">
+        <v>27</v>
+      </c>
       <c r="G291">
         <v>29</v>
       </c>
@@ -6981,6 +7725,9 @@
       <c r="E292">
         <v>45</v>
       </c>
+      <c r="F292">
+        <v>23</v>
+      </c>
       <c r="G292">
         <v>44</v>
       </c>
@@ -7004,6 +7751,9 @@
       <c r="E293">
         <v>42</v>
       </c>
+      <c r="F293">
+        <v>20</v>
+      </c>
       <c r="G293">
         <v>62</v>
       </c>
@@ -7027,6 +7777,9 @@
       <c r="E294">
         <v>44</v>
       </c>
+      <c r="F294">
+        <v>29</v>
+      </c>
       <c r="G294">
         <v>50</v>
       </c>
@@ -7050,6 +7803,9 @@
       <c r="E295">
         <v>44</v>
       </c>
+      <c r="F295">
+        <v>32</v>
+      </c>
       <c r="G295">
         <v>28</v>
       </c>
@@ -7073,11 +7829,14 @@
       <c r="E296">
         <v>538</v>
       </c>
+      <c r="F296">
+        <v>368</v>
+      </c>
       <c r="G296">
-        <v>780</v>
+        <v>795</v>
       </c>
       <c r="H296">
-        <v>4161</v>
+        <v>4214</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -7096,11 +7855,14 @@
       <c r="E297">
         <v>544</v>
       </c>
+      <c r="F297">
+        <v>345</v>
+      </c>
       <c r="G297">
-        <v>835</v>
+        <v>860</v>
       </c>
       <c r="H297">
-        <v>4220</v>
+        <v>4295</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -7119,11 +7881,14 @@
       <c r="E298">
         <v>554</v>
       </c>
+      <c r="F298">
+        <v>453</v>
+      </c>
       <c r="G298">
-        <v>855</v>
+        <v>876</v>
       </c>
       <c r="H298">
-        <v>4299</v>
+        <v>4349</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -7142,11 +7907,14 @@
       <c r="E299">
         <v>570</v>
       </c>
+      <c r="F299">
+        <v>395</v>
+      </c>
       <c r="G299">
-        <v>813</v>
+        <v>826</v>
       </c>
       <c r="H299">
-        <v>4399</v>
+        <v>4447</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -7165,11 +7933,14 @@
       <c r="E300">
         <v>605</v>
       </c>
+      <c r="F300">
+        <v>342</v>
+      </c>
       <c r="G300">
-        <v>821</v>
+        <v>837</v>
       </c>
       <c r="H300">
-        <v>4468</v>
+        <v>4518</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -7188,11 +7959,14 @@
       <c r="E301">
         <v>579</v>
       </c>
+      <c r="F301">
+        <v>396</v>
+      </c>
       <c r="G301">
-        <v>919</v>
+        <v>939</v>
       </c>
       <c r="H301">
-        <v>4563</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -7211,11 +7985,14 @@
       <c r="E302">
         <v>585</v>
       </c>
+      <c r="F302">
+        <v>371</v>
+      </c>
       <c r="G302">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="H302">
-        <v>4666</v>
+        <v>4719</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -7234,11 +8011,14 @@
       <c r="E303">
         <v>619</v>
       </c>
+      <c r="F303">
+        <v>399</v>
+      </c>
       <c r="G303">
         <v>888</v>
       </c>
       <c r="H303">
-        <v>4573</v>
+        <v>4588</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -7257,11 +8037,14 @@
       <c r="E304">
         <v>622</v>
       </c>
+      <c r="F304">
+        <v>436</v>
+      </c>
       <c r="G304">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="H304">
-        <v>4733</v>
+        <v>4746</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -7280,11 +8063,14 @@
       <c r="E305">
         <v>592</v>
       </c>
+      <c r="F305">
+        <v>375</v>
+      </c>
       <c r="G305">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="H305">
-        <v>4808</v>
+        <v>4811</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -7303,11 +8089,14 @@
       <c r="E306">
         <v>556</v>
       </c>
+      <c r="F306">
+        <v>446</v>
+      </c>
       <c r="G306">
         <v>543</v>
       </c>
       <c r="H306">
-        <v>4439</v>
+        <v>4441</v>
       </c>
     </row>
     <row r="307" spans="1:8">
@@ -7326,6 +8115,9 @@
       <c r="E307">
         <v>585</v>
       </c>
+      <c r="F307">
+        <v>441</v>
+      </c>
       <c r="G307">
         <v>896</v>
       </c>
@@ -7349,11 +8141,14 @@
       <c r="E308">
         <v>663</v>
       </c>
+      <c r="F308">
+        <v>378</v>
+      </c>
       <c r="G308">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H308">
-        <v>4707</v>
+        <v>4709</v>
       </c>
     </row>
     <row r="309" spans="1:8">
@@ -7372,11 +8167,14 @@
       <c r="E309">
         <v>676</v>
       </c>
+      <c r="F309">
+        <v>404</v>
+      </c>
       <c r="G309">
         <v>960</v>
       </c>
       <c r="H309">
-        <v>4847</v>
+        <v>4848</v>
       </c>
     </row>
     <row r="310" spans="1:8">
@@ -7395,11 +8193,14 @@
       <c r="E310">
         <v>35</v>
       </c>
+      <c r="F310">
+        <v>49</v>
+      </c>
       <c r="G310">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="H310">
-        <v>939</v>
+        <v>961</v>
       </c>
     </row>
     <row r="311" spans="1:8">
@@ -7418,11 +8219,14 @@
       <c r="E311">
         <v>100</v>
       </c>
+      <c r="F311">
+        <v>129</v>
+      </c>
       <c r="G311">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="H311">
-        <v>926</v>
+        <v>947</v>
       </c>
     </row>
     <row r="312" spans="1:8">
@@ -7441,11 +8245,14 @@
       <c r="E312">
         <v>110</v>
       </c>
+      <c r="F312">
+        <v>154</v>
+      </c>
       <c r="G312">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="H312">
-        <v>931</v>
+        <v>959</v>
       </c>
     </row>
     <row r="313" spans="1:8">
@@ -7464,11 +8271,14 @@
       <c r="E313">
         <v>121</v>
       </c>
+      <c r="F313">
+        <v>139</v>
+      </c>
       <c r="G313">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="H313">
-        <v>921</v>
+        <v>937</v>
       </c>
     </row>
     <row r="314" spans="1:8">
@@ -7487,11 +8297,14 @@
       <c r="E314">
         <v>96</v>
       </c>
+      <c r="F314">
+        <v>140</v>
+      </c>
       <c r="G314">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H314">
-        <v>942</v>
+        <v>960</v>
       </c>
     </row>
     <row r="315" spans="1:8">
@@ -7510,11 +8323,14 @@
       <c r="E315">
         <v>122</v>
       </c>
+      <c r="F315">
+        <v>122</v>
+      </c>
       <c r="G315">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="H315">
-        <v>937</v>
+        <v>955</v>
       </c>
     </row>
     <row r="316" spans="1:8">
@@ -7533,11 +8349,14 @@
       <c r="E316">
         <v>123</v>
       </c>
+      <c r="F316">
+        <v>131</v>
+      </c>
       <c r="G316">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="H316">
-        <v>966</v>
+        <v>981</v>
       </c>
     </row>
     <row r="317" spans="1:8">
@@ -7556,11 +8375,14 @@
       <c r="E317">
         <v>106</v>
       </c>
+      <c r="F317">
+        <v>131</v>
+      </c>
       <c r="G317">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H317">
-        <v>951</v>
+        <v>956</v>
       </c>
     </row>
     <row r="318" spans="1:8">
@@ -7579,11 +8401,14 @@
       <c r="E318">
         <v>151</v>
       </c>
+      <c r="F318">
+        <v>139</v>
+      </c>
       <c r="G318">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H318">
-        <v>1011</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="319" spans="1:8">
@@ -7602,6 +8427,9 @@
       <c r="E319">
         <v>112</v>
       </c>
+      <c r="F319">
+        <v>120</v>
+      </c>
       <c r="G319">
         <v>233</v>
       </c>
@@ -7625,11 +8453,14 @@
       <c r="E320">
         <v>123</v>
       </c>
+      <c r="F320">
+        <v>131</v>
+      </c>
       <c r="G320">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H320">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="321" spans="1:8">
@@ -7648,6 +8479,9 @@
       <c r="E321">
         <v>104</v>
       </c>
+      <c r="F321">
+        <v>127</v>
+      </c>
       <c r="G321">
         <v>310</v>
       </c>
@@ -7671,11 +8505,14 @@
       <c r="E322">
         <v>141</v>
       </c>
+      <c r="F322">
+        <v>150</v>
+      </c>
       <c r="G322">
         <v>277</v>
       </c>
       <c r="H322">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -7694,6 +8531,9 @@
       <c r="E323">
         <v>164</v>
       </c>
+      <c r="F323">
+        <v>162</v>
+      </c>
       <c r="G323">
         <v>272</v>
       </c>
@@ -7717,11 +8557,14 @@
       <c r="E324">
         <v>2</v>
       </c>
+      <c r="F324">
+        <v>4</v>
+      </c>
       <c r="G324">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H324">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -7740,11 +8583,14 @@
       <c r="E325">
         <v>16</v>
       </c>
+      <c r="F325">
+        <v>11</v>
+      </c>
       <c r="G325">
         <v>11</v>
       </c>
       <c r="H325">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -7763,11 +8609,14 @@
       <c r="E326">
         <v>20</v>
       </c>
+      <c r="F326">
+        <v>14</v>
+      </c>
       <c r="G326">
         <v>25</v>
       </c>
       <c r="H326">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -7786,6 +8635,9 @@
       <c r="E327">
         <v>11</v>
       </c>
+      <c r="F327">
+        <v>7</v>
+      </c>
       <c r="G327">
         <v>30</v>
       </c>
@@ -7809,11 +8661,14 @@
       <c r="E328">
         <v>19</v>
       </c>
+      <c r="F328">
+        <v>12</v>
+      </c>
       <c r="G328">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H328">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="329" spans="1:8">
@@ -7832,6 +8687,9 @@
       <c r="E329">
         <v>16</v>
       </c>
+      <c r="F329">
+        <v>12</v>
+      </c>
       <c r="G329">
         <v>22</v>
       </c>
@@ -7855,6 +8713,9 @@
       <c r="E330">
         <v>16</v>
       </c>
+      <c r="F330">
+        <v>15</v>
+      </c>
       <c r="G330">
         <v>34</v>
       </c>
@@ -7878,6 +8739,9 @@
       <c r="E331">
         <v>16</v>
       </c>
+      <c r="F331">
+        <v>17</v>
+      </c>
       <c r="G331">
         <v>27</v>
       </c>
@@ -7901,6 +8765,9 @@
       <c r="E332">
         <v>16</v>
       </c>
+      <c r="F332">
+        <v>22</v>
+      </c>
       <c r="G332">
         <v>43</v>
       </c>
@@ -7924,6 +8791,9 @@
       <c r="E333">
         <v>24</v>
       </c>
+      <c r="F333">
+        <v>12</v>
+      </c>
       <c r="G333">
         <v>38</v>
       </c>
@@ -7947,6 +8817,9 @@
       <c r="E334">
         <v>22</v>
       </c>
+      <c r="F334">
+        <v>17</v>
+      </c>
       <c r="G334">
         <v>51</v>
       </c>
@@ -7970,6 +8843,9 @@
       <c r="E335">
         <v>12</v>
       </c>
+      <c r="F335">
+        <v>14</v>
+      </c>
       <c r="G335">
         <v>56</v>
       </c>
@@ -7993,6 +8869,9 @@
       <c r="E336">
         <v>16</v>
       </c>
+      <c r="F336">
+        <v>29</v>
+      </c>
       <c r="G336">
         <v>55</v>
       </c>
@@ -8016,6 +8895,9 @@
       <c r="E337">
         <v>33</v>
       </c>
+      <c r="F337">
+        <v>24</v>
+      </c>
       <c r="G337">
         <v>47</v>
       </c>
@@ -8039,11 +8921,14 @@
       <c r="E338">
         <v>1</v>
       </c>
+      <c r="F338">
+        <v>2</v>
+      </c>
       <c r="G338">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H338">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="339" spans="1:8">
@@ -8062,6 +8947,9 @@
       <c r="E339">
         <v>4</v>
       </c>
+      <c r="F339">
+        <v>3</v>
+      </c>
       <c r="G339">
         <v>5</v>
       </c>
@@ -8085,11 +8973,14 @@
       <c r="E340">
         <v>2</v>
       </c>
+      <c r="F340">
+        <v>2</v>
+      </c>
       <c r="G340">
         <v>2</v>
       </c>
       <c r="H340">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="341" spans="1:8">
@@ -8108,6 +8999,9 @@
       <c r="E341">
         <v>4</v>
       </c>
+      <c r="F341">
+        <v>6</v>
+      </c>
       <c r="G341">
         <v>4</v>
       </c>
@@ -8131,6 +9025,9 @@
       <c r="E342">
         <v>2</v>
       </c>
+      <c r="F342">
+        <v>1</v>
+      </c>
       <c r="G342">
         <v>5</v>
       </c>
@@ -8154,6 +9051,9 @@
       <c r="E343">
         <v>4</v>
       </c>
+      <c r="F343">
+        <v>3</v>
+      </c>
       <c r="G343">
         <v>6</v>
       </c>
@@ -8177,6 +9077,9 @@
       <c r="E344">
         <v>5</v>
       </c>
+      <c r="F344">
+        <v>1</v>
+      </c>
       <c r="G344">
         <v>11</v>
       </c>
@@ -8200,11 +9103,14 @@
       <c r="E345">
         <v>3</v>
       </c>
+      <c r="F345">
+        <v>5</v>
+      </c>
       <c r="G345">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H345">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="346" spans="1:8">
@@ -8223,6 +9129,9 @@
       <c r="E346">
         <v>3</v>
       </c>
+      <c r="F346">
+        <v>2</v>
+      </c>
       <c r="G346">
         <v>7</v>
       </c>
@@ -8246,6 +9155,9 @@
       <c r="E347">
         <v>1</v>
       </c>
+      <c r="F347">
+        <v>3</v>
+      </c>
       <c r="G347">
         <v>7</v>
       </c>
@@ -8269,6 +9181,9 @@
       <c r="E348">
         <v>2</v>
       </c>
+      <c r="F348">
+        <v>6</v>
+      </c>
       <c r="G348">
         <v>14</v>
       </c>
@@ -8292,6 +9207,9 @@
       <c r="E349">
         <v>4</v>
       </c>
+      <c r="F349">
+        <v>3</v>
+      </c>
       <c r="G349">
         <v>15</v>
       </c>
@@ -8315,6 +9233,9 @@
       <c r="E350">
         <v>5</v>
       </c>
+      <c r="F350">
+        <v>5</v>
+      </c>
       <c r="G350">
         <v>14</v>
       </c>
@@ -8338,6 +9259,9 @@
       <c r="E351">
         <v>4</v>
       </c>
+      <c r="F351">
+        <v>4</v>
+      </c>
       <c r="G351">
         <v>13</v>
       </c>
@@ -8361,6 +9285,9 @@
       <c r="E352">
         <v>3</v>
       </c>
+      <c r="F352">
+        <v>4</v>
+      </c>
       <c r="G352">
         <v>4</v>
       </c>
@@ -8384,11 +9311,14 @@
       <c r="E353">
         <v>6</v>
       </c>
+      <c r="F353">
+        <v>3</v>
+      </c>
       <c r="G353">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H353">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="354" spans="1:8">
@@ -8407,11 +9337,14 @@
       <c r="E354">
         <v>5</v>
       </c>
+      <c r="F354">
+        <v>7</v>
+      </c>
       <c r="G354">
         <v>11</v>
       </c>
       <c r="H354">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -8430,6 +9363,9 @@
       <c r="E355">
         <v>7</v>
       </c>
+      <c r="F355">
+        <v>5</v>
+      </c>
       <c r="G355">
         <v>16</v>
       </c>
@@ -8453,11 +9389,14 @@
       <c r="E356">
         <v>6</v>
       </c>
+      <c r="F356">
+        <v>5</v>
+      </c>
       <c r="G356">
         <v>18</v>
       </c>
       <c r="H356">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -8476,11 +9415,14 @@
       <c r="E357">
         <v>10</v>
       </c>
+      <c r="F357">
+        <v>10</v>
+      </c>
       <c r="G357">
         <v>13</v>
       </c>
       <c r="H357">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="358" spans="1:8">
@@ -8499,11 +9441,14 @@
       <c r="E358">
         <v>5</v>
       </c>
+      <c r="F358">
+        <v>8</v>
+      </c>
       <c r="G358">
         <v>19</v>
       </c>
       <c r="H358">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -8522,11 +9467,14 @@
       <c r="E359">
         <v>7</v>
       </c>
+      <c r="F359">
+        <v>11</v>
+      </c>
       <c r="G359">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H359">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="360" spans="1:8">
@@ -8545,11 +9493,14 @@
       <c r="E360">
         <v>7</v>
       </c>
+      <c r="F360">
+        <v>13</v>
+      </c>
       <c r="G360">
         <v>31</v>
       </c>
       <c r="H360">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="361" spans="1:8">
@@ -8568,6 +9519,9 @@
       <c r="E361">
         <v>10</v>
       </c>
+      <c r="F361">
+        <v>16</v>
+      </c>
       <c r="G361">
         <v>31</v>
       </c>
@@ -8591,6 +9545,9 @@
       <c r="E362">
         <v>14</v>
       </c>
+      <c r="F362">
+        <v>20</v>
+      </c>
       <c r="G362">
         <v>47</v>
       </c>
@@ -8614,6 +9571,9 @@
       <c r="E363">
         <v>11</v>
       </c>
+      <c r="F363">
+        <v>19</v>
+      </c>
       <c r="G363">
         <v>73</v>
       </c>
@@ -8637,6 +9597,9 @@
       <c r="E364">
         <v>15</v>
       </c>
+      <c r="F364">
+        <v>22</v>
+      </c>
       <c r="G364">
         <v>43</v>
       </c>
@@ -8660,6 +9623,9 @@
       <c r="E365">
         <v>15</v>
       </c>
+      <c r="F365">
+        <v>21</v>
+      </c>
       <c r="G365">
         <v>52</v>
       </c>
@@ -8683,6 +9649,9 @@
       <c r="E366">
         <v>0</v>
       </c>
+      <c r="F366">
+        <v>0</v>
+      </c>
       <c r="G366">
         <v>0</v>
       </c>
@@ -8706,6 +9675,9 @@
       <c r="E367">
         <v>0</v>
       </c>
+      <c r="F367">
+        <v>1</v>
+      </c>
       <c r="G367">
         <v>1</v>
       </c>
@@ -8729,6 +9701,9 @@
       <c r="E368">
         <v>0</v>
       </c>
+      <c r="F368">
+        <v>1</v>
+      </c>
       <c r="G368">
         <v>0</v>
       </c>
@@ -8752,6 +9727,9 @@
       <c r="E369">
         <v>0</v>
       </c>
+      <c r="F369">
+        <v>0</v>
+      </c>
       <c r="G369">
         <v>0</v>
       </c>
@@ -8775,11 +9753,14 @@
       <c r="E370">
         <v>2</v>
       </c>
+      <c r="F370">
+        <v>0</v>
+      </c>
       <c r="G370">
         <v>0</v>
       </c>
       <c r="H370">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371" spans="1:8">
@@ -8798,6 +9779,9 @@
       <c r="E371">
         <v>0</v>
       </c>
+      <c r="F371">
+        <v>0</v>
+      </c>
       <c r="G371">
         <v>2</v>
       </c>
@@ -8821,6 +9805,9 @@
       <c r="E372">
         <v>0</v>
       </c>
+      <c r="F372">
+        <v>0</v>
+      </c>
       <c r="G372">
         <v>0</v>
       </c>
@@ -8844,6 +9831,9 @@
       <c r="E373">
         <v>0</v>
       </c>
+      <c r="F373">
+        <v>2</v>
+      </c>
       <c r="G373">
         <v>0</v>
       </c>
@@ -8867,6 +9857,9 @@
       <c r="E374">
         <v>1</v>
       </c>
+      <c r="F374">
+        <v>0</v>
+      </c>
       <c r="G374">
         <v>0</v>
       </c>
@@ -8890,6 +9883,9 @@
       <c r="E375">
         <v>0</v>
       </c>
+      <c r="F375">
+        <v>0</v>
+      </c>
       <c r="G375">
         <v>1</v>
       </c>
@@ -8913,6 +9909,9 @@
       <c r="E376">
         <v>0</v>
       </c>
+      <c r="F376">
+        <v>0</v>
+      </c>
       <c r="G376">
         <v>0</v>
       </c>
@@ -8936,6 +9935,9 @@
       <c r="E377">
         <v>0</v>
       </c>
+      <c r="F377">
+        <v>1</v>
+      </c>
       <c r="G377">
         <v>0</v>
       </c>
@@ -8959,6 +9961,9 @@
       <c r="E378">
         <v>0</v>
       </c>
+      <c r="F378">
+        <v>0</v>
+      </c>
       <c r="G378">
         <v>0</v>
       </c>
@@ -8982,6 +9987,9 @@
       <c r="E379">
         <v>0</v>
       </c>
+      <c r="F379">
+        <v>0</v>
+      </c>
       <c r="G379">
         <v>0</v>
       </c>
@@ -9005,6 +10013,9 @@
       <c r="E380">
         <v>0</v>
       </c>
+      <c r="F380">
+        <v>2</v>
+      </c>
       <c r="G380">
         <v>8</v>
       </c>
@@ -9028,6 +10039,9 @@
       <c r="E381">
         <v>1</v>
       </c>
+      <c r="F381">
+        <v>1</v>
+      </c>
       <c r="G381">
         <v>9</v>
       </c>
@@ -9051,6 +10065,9 @@
       <c r="E382">
         <v>2</v>
       </c>
+      <c r="F382">
+        <v>3</v>
+      </c>
       <c r="G382">
         <v>5</v>
       </c>
@@ -9074,6 +10091,9 @@
       <c r="E383">
         <v>2</v>
       </c>
+      <c r="F383">
+        <v>6</v>
+      </c>
       <c r="G383">
         <v>13</v>
       </c>
@@ -9097,11 +10117,14 @@
       <c r="E384">
         <v>2</v>
       </c>
+      <c r="F384">
+        <v>8</v>
+      </c>
       <c r="G384">
         <v>9</v>
       </c>
       <c r="H384">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="385" spans="1:8">
@@ -9120,11 +10143,14 @@
       <c r="E385">
         <v>1</v>
       </c>
+      <c r="F385">
+        <v>5</v>
+      </c>
       <c r="G385">
         <v>7</v>
       </c>
       <c r="H385">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="386" spans="1:8">
@@ -9143,11 +10169,14 @@
       <c r="E386">
         <v>7</v>
       </c>
+      <c r="F386">
+        <v>7</v>
+      </c>
       <c r="G386">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H386">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="387" spans="1:8">
@@ -9166,6 +10195,9 @@
       <c r="E387">
         <v>5</v>
       </c>
+      <c r="F387">
+        <v>6</v>
+      </c>
       <c r="G387">
         <v>15</v>
       </c>
@@ -9189,6 +10221,9 @@
       <c r="E388">
         <v>5</v>
       </c>
+      <c r="F388">
+        <v>11</v>
+      </c>
       <c r="G388">
         <v>18</v>
       </c>
@@ -9212,6 +10247,9 @@
       <c r="E389">
         <v>6</v>
       </c>
+      <c r="F389">
+        <v>7</v>
+      </c>
       <c r="G389">
         <v>15</v>
       </c>
@@ -9235,6 +10273,9 @@
       <c r="E390">
         <v>3</v>
       </c>
+      <c r="F390">
+        <v>11</v>
+      </c>
       <c r="G390">
         <v>22</v>
       </c>
@@ -9258,6 +10299,9 @@
       <c r="E391">
         <v>5</v>
       </c>
+      <c r="F391">
+        <v>10</v>
+      </c>
       <c r="G391">
         <v>19</v>
       </c>
@@ -9281,6 +10325,9 @@
       <c r="E392">
         <v>10</v>
       </c>
+      <c r="F392">
+        <v>7</v>
+      </c>
       <c r="G392">
         <v>28</v>
       </c>
@@ -9304,6 +10351,9 @@
       <c r="E393">
         <v>6</v>
       </c>
+      <c r="F393">
+        <v>16</v>
+      </c>
       <c r="G393">
         <v>22</v>
       </c>
@@ -9327,8 +10377,11 @@
       <c r="E394">
         <v>17</v>
       </c>
+      <c r="F394">
+        <v>15</v>
+      </c>
       <c r="G394">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="395" spans="1:8">
@@ -9347,6 +10400,9 @@
       <c r="E395">
         <v>17</v>
       </c>
+      <c r="F395">
+        <v>19</v>
+      </c>
       <c r="G395">
         <v>13</v>
       </c>
@@ -9367,6 +10423,9 @@
       <c r="E396">
         <v>21</v>
       </c>
+      <c r="F396">
+        <v>11</v>
+      </c>
       <c r="G396">
         <v>12</v>
       </c>
@@ -9387,8 +10446,11 @@
       <c r="E397">
         <v>19</v>
       </c>
+      <c r="F397">
+        <v>13</v>
+      </c>
       <c r="G397">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="398" spans="1:8">
@@ -9407,6 +10469,9 @@
       <c r="E398">
         <v>18</v>
       </c>
+      <c r="F398">
+        <v>13</v>
+      </c>
       <c r="G398">
         <v>7</v>
       </c>
@@ -9427,6 +10492,9 @@
       <c r="E399">
         <v>21</v>
       </c>
+      <c r="F399">
+        <v>6</v>
+      </c>
       <c r="G399">
         <v>14</v>
       </c>
@@ -9447,6 +10515,9 @@
       <c r="E400">
         <v>15</v>
       </c>
+      <c r="F400">
+        <v>10</v>
+      </c>
       <c r="G400">
         <v>13</v>
       </c>
@@ -9467,11 +10538,14 @@
       <c r="E401">
         <v>14</v>
       </c>
+      <c r="F401">
+        <v>6</v>
+      </c>
       <c r="G401">
         <v>15</v>
       </c>
       <c r="H401">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="402" spans="1:8">
@@ -9490,6 +10564,9 @@
       <c r="E402">
         <v>10</v>
       </c>
+      <c r="F402">
+        <v>12</v>
+      </c>
       <c r="G402">
         <v>11</v>
       </c>
@@ -9513,6 +10590,9 @@
       <c r="E403">
         <v>13</v>
       </c>
+      <c r="F403">
+        <v>8</v>
+      </c>
       <c r="G403">
         <v>7</v>
       </c>
@@ -9536,6 +10616,9 @@
       <c r="E404">
         <v>18</v>
       </c>
+      <c r="F404">
+        <v>12</v>
+      </c>
       <c r="G404">
         <v>14</v>
       </c>
@@ -9559,6 +10642,9 @@
       <c r="E405">
         <v>9</v>
       </c>
+      <c r="F405">
+        <v>8</v>
+      </c>
       <c r="G405">
         <v>17</v>
       </c>
@@ -9582,6 +10668,9 @@
       <c r="E406">
         <v>14</v>
       </c>
+      <c r="F406">
+        <v>2</v>
+      </c>
       <c r="G406">
         <v>15</v>
       </c>
@@ -9605,11 +10694,14 @@
       <c r="E407">
         <v>9</v>
       </c>
+      <c r="F407">
+        <v>7</v>
+      </c>
       <c r="G407">
         <v>12</v>
       </c>
       <c r="H407">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="408" spans="1:8">
@@ -9628,11 +10720,14 @@
       <c r="E408">
         <v>140</v>
       </c>
+      <c r="F408">
+        <v>118</v>
+      </c>
       <c r="G408">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="H408">
-        <v>1155</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="409" spans="1:8">
@@ -9651,11 +10746,14 @@
       <c r="E409">
         <v>118</v>
       </c>
+      <c r="F409">
+        <v>126</v>
+      </c>
       <c r="G409">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="H409">
-        <v>1208</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="410" spans="1:8">
@@ -9674,11 +10772,14 @@
       <c r="E410">
         <v>153</v>
       </c>
+      <c r="F410">
+        <v>116</v>
+      </c>
       <c r="G410">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="H410">
-        <v>1246</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="411" spans="1:8">
@@ -9697,11 +10798,14 @@
       <c r="E411">
         <v>141</v>
       </c>
+      <c r="F411">
+        <v>108</v>
+      </c>
       <c r="G411">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H411">
-        <v>1242</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="412" spans="1:8">
@@ -9720,11 +10824,14 @@
       <c r="E412">
         <v>146</v>
       </c>
+      <c r="F412">
+        <v>139</v>
+      </c>
       <c r="G412">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="H412">
-        <v>1286</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="413" spans="1:8">
@@ -9743,11 +10850,14 @@
       <c r="E413">
         <v>160</v>
       </c>
+      <c r="F413">
+        <v>155</v>
+      </c>
       <c r="G413">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="H413">
-        <v>1293</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="414" spans="1:8">
@@ -9766,11 +10876,14 @@
       <c r="E414">
         <v>138</v>
       </c>
+      <c r="F414">
+        <v>122</v>
+      </c>
       <c r="G414">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H414">
-        <v>1326</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="415" spans="1:8">
@@ -9789,11 +10902,14 @@
       <c r="E415">
         <v>145</v>
       </c>
+      <c r="F415">
+        <v>143</v>
+      </c>
       <c r="G415">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H415">
-        <v>1336</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="416" spans="1:8">
@@ -9812,11 +10928,14 @@
       <c r="E416">
         <v>175</v>
       </c>
+      <c r="F416">
+        <v>170</v>
+      </c>
       <c r="G416">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H416">
-        <v>1395</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="417" spans="1:8">
@@ -9835,11 +10954,14 @@
       <c r="E417">
         <v>178</v>
       </c>
+      <c r="F417">
+        <v>129</v>
+      </c>
       <c r="G417">
         <v>263</v>
       </c>
       <c r="H417">
-        <v>1392</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="418" spans="1:8">
@@ -9858,6 +10980,9 @@
       <c r="E418">
         <v>154</v>
       </c>
+      <c r="F418">
+        <v>136</v>
+      </c>
       <c r="G418">
         <v>170</v>
       </c>
@@ -9881,6 +11006,9 @@
       <c r="E419">
         <v>175</v>
       </c>
+      <c r="F419">
+        <v>133</v>
+      </c>
       <c r="G419">
         <v>316</v>
       </c>
@@ -9904,6 +11032,9 @@
       <c r="E420">
         <v>178</v>
       </c>
+      <c r="F420">
+        <v>116</v>
+      </c>
       <c r="G420">
         <v>342</v>
       </c>
@@ -9927,6 +11058,9 @@
       <c r="E421">
         <v>166</v>
       </c>
+      <c r="F421">
+        <v>125</v>
+      </c>
       <c r="G421">
         <v>396</v>
       </c>
@@ -10070,10 +11204,10 @@
         <v>704</v>
       </c>
       <c r="G429">
-        <v>933</v>
+        <v>940</v>
       </c>
       <c r="H429">
-        <v>4925</v>
+        <v>4957</v>
       </c>
     </row>
     <row r="430" spans="1:8">
@@ -10093,10 +11227,10 @@
         <v>708</v>
       </c>
       <c r="G430">
-        <v>981</v>
+        <v>991</v>
       </c>
       <c r="H430">
-        <v>5125</v>
+        <v>5158</v>
       </c>
     </row>
     <row r="431" spans="1:8">
@@ -10116,10 +11250,10 @@
         <v>707</v>
       </c>
       <c r="G431">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H431">
-        <v>5093</v>
+        <v>5094</v>
       </c>
     </row>
     <row r="432" spans="1:8">
@@ -10185,10 +11319,10 @@
         <v>694</v>
       </c>
       <c r="G434">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="H434">
-        <v>5066</v>
+        <v>5069</v>
       </c>
     </row>
     <row r="435" spans="1:8">
@@ -10211,7 +11345,7 @@
         <v>851</v>
       </c>
       <c r="H435">
-        <v>5033</v>
+        <v>5034</v>
       </c>
     </row>
     <row r="436" spans="1:8">
@@ -10422,7 +11556,7 @@
         <v>125</v>
       </c>
       <c r="H446">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="447" spans="1:8">
@@ -10633,7 +11767,7 @@
         <v>36</v>
       </c>
       <c r="H457">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="458" spans="1:8">
@@ -10656,7 +11790,7 @@
         <v>39</v>
       </c>
       <c r="H458">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="459" spans="1:8">
@@ -10748,7 +11882,7 @@
         <v>40</v>
       </c>
       <c r="H462">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="463" spans="1:8">
@@ -10771,7 +11905,7 @@
         <v>39</v>
       </c>
       <c r="H463">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="464" spans="1:8">
@@ -10910,10 +12044,10 @@
         <v>51</v>
       </c>
       <c r="G471">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H471">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="472" spans="1:8">
@@ -10936,7 +12070,7 @@
         <v>118</v>
       </c>
       <c r="H472">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="473" spans="1:8">
@@ -10959,7 +12093,7 @@
         <v>141</v>
       </c>
       <c r="H473">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="474" spans="1:8">
@@ -11028,7 +12162,7 @@
         <v>140</v>
       </c>
       <c r="H476">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="477" spans="1:8">
@@ -11470,10 +12604,10 @@
         <v>13</v>
       </c>
       <c r="G499">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H499">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="500" spans="1:8">
@@ -11496,7 +12630,7 @@
         <v>48</v>
       </c>
       <c r="H500">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="501" spans="1:8">
@@ -11891,7 +13025,7 @@
         <v>31</v>
       </c>
       <c r="H519">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="520" spans="1:8">
@@ -12033,7 +13167,7 @@
         <v>1012</v>
       </c>
       <c r="H527">
-        <v>5556</v>
+        <v>5570</v>
       </c>
     </row>
     <row r="528" spans="1:8">
@@ -12053,10 +13187,10 @@
         <v>797</v>
       </c>
       <c r="G528">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="H528">
-        <v>5710</v>
+        <v>5724</v>
       </c>
     </row>
     <row r="529" spans="1:8">
@@ -12076,10 +13210,10 @@
         <v>770</v>
       </c>
       <c r="G529">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="H529">
-        <v>5815</v>
+        <v>5818</v>
       </c>
     </row>
     <row r="530" spans="1:8">
@@ -12102,7 +13236,7 @@
         <v>630</v>
       </c>
       <c r="H530">
-        <v>5482</v>
+        <v>5484</v>
       </c>
     </row>
     <row r="531" spans="1:8">
@@ -12145,10 +13279,10 @@
         <v>841</v>
       </c>
       <c r="G532">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H532">
-        <v>5907</v>
+        <v>5909</v>
       </c>
     </row>
     <row r="533" spans="1:8">
@@ -12171,7 +13305,7 @@
         <v>1211</v>
       </c>
       <c r="H533">
-        <v>6233</v>
+        <v>6234</v>
       </c>
     </row>
     <row r="534" spans="1:8">
@@ -12310,10 +13444,10 @@
         <v>598</v>
       </c>
       <c r="G541">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="H541">
-        <v>4043</v>
+        <v>4071</v>
       </c>
     </row>
     <row r="542" spans="1:8">
@@ -12333,10 +13467,10 @@
         <v>557</v>
       </c>
       <c r="G542">
-        <v>781</v>
+        <v>790</v>
       </c>
       <c r="H542">
-        <v>4177</v>
+        <v>4207</v>
       </c>
     </row>
     <row r="543" spans="1:8">
@@ -12356,10 +13490,10 @@
         <v>595</v>
       </c>
       <c r="G543">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H543">
-        <v>4103</v>
+        <v>4104</v>
       </c>
     </row>
     <row r="544" spans="1:8">
@@ -12425,10 +13559,10 @@
         <v>553</v>
       </c>
       <c r="G546">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="H546">
-        <v>3860</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="547" spans="1:8">
@@ -12451,7 +13585,7 @@
         <v>614</v>
       </c>
       <c r="H547">
-        <v>3792</v>
+        <v>3793</v>
       </c>
     </row>
     <row r="548" spans="1:8">
@@ -12662,7 +13796,7 @@
         <v>81</v>
       </c>
       <c r="H558">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="559" spans="1:8">
@@ -12873,7 +14007,7 @@
         <v>28</v>
       </c>
       <c r="H569">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="570" spans="1:8">
@@ -12896,7 +14030,7 @@
         <v>36</v>
       </c>
       <c r="H570">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="571" spans="1:8">
@@ -12988,7 +14122,7 @@
         <v>32</v>
       </c>
       <c r="H574">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="575" spans="1:8">
@@ -13011,7 +14145,7 @@
         <v>28</v>
       </c>
       <c r="H575">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="576" spans="1:8">
@@ -13153,7 +14287,7 @@
         <v>95</v>
       </c>
       <c r="H583">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="584" spans="1:8">
@@ -13176,7 +14310,7 @@
         <v>96</v>
       </c>
       <c r="H584">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="585" spans="1:8">
@@ -13199,7 +14333,7 @@
         <v>112</v>
       </c>
       <c r="H585">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="586" spans="1:8">
@@ -13268,7 +14402,7 @@
         <v>101</v>
       </c>
       <c r="H588">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="589" spans="1:8">
@@ -13710,10 +14844,10 @@
         <v>8</v>
       </c>
       <c r="G611">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H611">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="612" spans="1:8">
@@ -13736,7 +14870,7 @@
         <v>33</v>
       </c>
       <c r="H612">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="613" spans="1:8">
@@ -14273,7 +15407,7 @@
         <v>785</v>
       </c>
       <c r="H639">
-        <v>4317</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="640" spans="1:8">
@@ -14293,10 +15427,10 @@
         <v>622</v>
       </c>
       <c r="G640">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="H640">
-        <v>4406</v>
+        <v>4418</v>
       </c>
     </row>
     <row r="641" spans="1:8">
@@ -14316,10 +15450,10 @@
         <v>592</v>
       </c>
       <c r="G641">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="H641">
-        <v>4512</v>
+        <v>4514</v>
       </c>
     </row>
     <row r="642" spans="1:8">
@@ -14342,7 +15476,7 @@
         <v>478</v>
       </c>
       <c r="H642">
-        <v>4226</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="643" spans="1:8">
@@ -14385,10 +15519,10 @@
         <v>663</v>
       </c>
       <c r="G644">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H644">
-        <v>4442</v>
+        <v>4444</v>
       </c>
     </row>
     <row r="645" spans="1:8">
@@ -14411,7 +15545,7 @@
         <v>864</v>
       </c>
       <c r="H645">
-        <v>4627</v>
+        <v>4628</v>
       </c>
     </row>
     <row r="646" spans="1:8">
@@ -14550,10 +15684,10 @@
         <v>106</v>
       </c>
       <c r="G653">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H653">
-        <v>882</v>
+        <v>886</v>
       </c>
     </row>
     <row r="654" spans="1:8">
@@ -14573,10 +15707,10 @@
         <v>151</v>
       </c>
       <c r="G654">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H654">
-        <v>948</v>
+        <v>951</v>
       </c>
     </row>
     <row r="655" spans="1:8">
@@ -14668,7 +15802,7 @@
         <v>245</v>
       </c>
       <c r="H658">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="659" spans="1:8">
@@ -15390,10 +16524,10 @@
         <v>7</v>
       </c>
       <c r="G695">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H695">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="696" spans="1:8">
@@ -15416,7 +16550,7 @@
         <v>22</v>
       </c>
       <c r="H696">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="697" spans="1:8">
@@ -16371,7 +17505,7 @@
         <v>11</v>
       </c>
       <c r="H743">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="744" spans="1:8">
@@ -16513,7 +17647,7 @@
         <v>227</v>
       </c>
       <c r="H751">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="752" spans="1:8">
@@ -16533,10 +17667,10 @@
         <v>175</v>
       </c>
       <c r="G752">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H752">
-        <v>1304</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="753" spans="1:8">
@@ -16559,7 +17693,7 @@
         <v>228</v>
       </c>
       <c r="H753">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="754" spans="1:8">
@@ -16667,6 +17801,9 @@
       <c r="D758" t="s">
         <v>8</v>
       </c>
+      <c r="F758">
+        <v>1339</v>
+      </c>
     </row>
     <row r="759" spans="1:8">
       <c r="A759">
@@ -16681,6 +17818,9 @@
       <c r="D759" t="s">
         <v>8</v>
       </c>
+      <c r="F759">
+        <v>1306</v>
+      </c>
     </row>
     <row r="760" spans="1:8">
       <c r="A760">
@@ -16695,6 +17835,9 @@
       <c r="D760" t="s">
         <v>8</v>
       </c>
+      <c r="F760">
+        <v>1440</v>
+      </c>
     </row>
     <row r="761" spans="1:8">
       <c r="A761">
@@ -16709,6 +17852,9 @@
       <c r="D761" t="s">
         <v>8</v>
       </c>
+      <c r="F761">
+        <v>1475</v>
+      </c>
     </row>
     <row r="762" spans="1:8">
       <c r="A762">
@@ -16723,6 +17869,9 @@
       <c r="D762" t="s">
         <v>8</v>
       </c>
+      <c r="F762">
+        <v>1412</v>
+      </c>
     </row>
     <row r="763" spans="1:8">
       <c r="A763">
@@ -16737,6 +17886,9 @@
       <c r="D763" t="s">
         <v>8</v>
       </c>
+      <c r="F763">
+        <v>1430</v>
+      </c>
     </row>
     <row r="764" spans="1:8">
       <c r="A764">
@@ -16751,6 +17903,9 @@
       <c r="D764" t="s">
         <v>8</v>
       </c>
+      <c r="F764">
+        <v>1376</v>
+      </c>
     </row>
     <row r="765" spans="1:8">
       <c r="A765">
@@ -16765,11 +17920,14 @@
       <c r="D765" t="s">
         <v>8</v>
       </c>
+      <c r="F765">
+        <v>1355</v>
+      </c>
       <c r="G765">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="H765">
-        <v>824</v>
+        <v>849</v>
       </c>
     </row>
     <row r="766" spans="1:8">
@@ -16785,11 +17943,14 @@
       <c r="D766" t="s">
         <v>8</v>
       </c>
+      <c r="F766">
+        <v>1584</v>
+      </c>
       <c r="G766">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="H766">
-        <v>905</v>
+        <v>929</v>
       </c>
     </row>
     <row r="767" spans="1:8">
@@ -16805,11 +17966,14 @@
       <c r="D767" t="s">
         <v>8</v>
       </c>
+      <c r="F767">
+        <v>1375</v>
+      </c>
       <c r="G767">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="H767">
-        <v>916</v>
+        <v>922</v>
       </c>
     </row>
     <row r="768" spans="1:8">
@@ -16825,11 +17989,14 @@
       <c r="D768" t="s">
         <v>8</v>
       </c>
+      <c r="F768">
+        <v>1477</v>
+      </c>
       <c r="G768">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H768">
-        <v>852</v>
+        <v>856</v>
       </c>
     </row>
     <row r="769" spans="1:8">
@@ -16845,6 +18012,9 @@
       <c r="D769" t="s">
         <v>8</v>
       </c>
+      <c r="F769">
+        <v>1382</v>
+      </c>
       <c r="G769">
         <v>394</v>
       </c>
@@ -16865,11 +18035,14 @@
       <c r="D770" t="s">
         <v>8</v>
       </c>
+      <c r="F770">
+        <v>1430</v>
+      </c>
       <c r="G770">
         <v>361</v>
       </c>
       <c r="H770">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="771" spans="1:8">
@@ -16885,11 +18058,14 @@
       <c r="D771" t="s">
         <v>8</v>
       </c>
+      <c r="F771">
+        <v>1480</v>
+      </c>
       <c r="G771">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H771">
-        <v>822</v>
+        <v>824</v>
       </c>
     </row>
     <row r="772" spans="1:8">
@@ -16905,6 +18081,9 @@
       <c r="D772" t="s">
         <v>13</v>
       </c>
+      <c r="F772">
+        <v>258</v>
+      </c>
     </row>
     <row r="773" spans="1:8">
       <c r="A773">
@@ -16919,6 +18098,9 @@
       <c r="D773" t="s">
         <v>13</v>
       </c>
+      <c r="F773">
+        <v>655</v>
+      </c>
     </row>
     <row r="774" spans="1:8">
       <c r="A774">
@@ -16933,6 +18115,9 @@
       <c r="D774" t="s">
         <v>13</v>
       </c>
+      <c r="F774">
+        <v>669</v>
+      </c>
     </row>
     <row r="775" spans="1:8">
       <c r="A775">
@@ -16947,6 +18132,9 @@
       <c r="D775" t="s">
         <v>13</v>
       </c>
+      <c r="F775">
+        <v>743</v>
+      </c>
     </row>
     <row r="776" spans="1:8">
       <c r="A776">
@@ -16961,6 +18149,9 @@
       <c r="D776" t="s">
         <v>13</v>
       </c>
+      <c r="F776">
+        <v>749</v>
+      </c>
     </row>
     <row r="777" spans="1:8">
       <c r="A777">
@@ -16975,6 +18166,9 @@
       <c r="D777" t="s">
         <v>13</v>
       </c>
+      <c r="F777">
+        <v>665</v>
+      </c>
     </row>
     <row r="778" spans="1:8">
       <c r="A778">
@@ -16989,6 +18183,9 @@
       <c r="D778" t="s">
         <v>13</v>
       </c>
+      <c r="F778">
+        <v>673</v>
+      </c>
     </row>
     <row r="779" spans="1:8">
       <c r="A779">
@@ -17003,11 +18200,14 @@
       <c r="D779" t="s">
         <v>13</v>
       </c>
+      <c r="F779">
+        <v>606</v>
+      </c>
       <c r="G779">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H779">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="780" spans="1:8">
@@ -17023,11 +18223,14 @@
       <c r="D780" t="s">
         <v>13</v>
       </c>
+      <c r="F780">
+        <v>738</v>
+      </c>
       <c r="G780">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="H780">
-        <v>281</v>
+        <v>299</v>
       </c>
     </row>
     <row r="781" spans="1:8">
@@ -17043,11 +18246,14 @@
       <c r="D781" t="s">
         <v>13</v>
       </c>
+      <c r="F781">
+        <v>645</v>
+      </c>
       <c r="G781">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H781">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="782" spans="1:8">
@@ -17063,11 +18269,14 @@
       <c r="D782" t="s">
         <v>13</v>
       </c>
+      <c r="F782">
+        <v>654</v>
+      </c>
       <c r="G782">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H782">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="783" spans="1:8">
@@ -17083,6 +18292,9 @@
       <c r="D783" t="s">
         <v>13</v>
       </c>
+      <c r="F783">
+        <v>576</v>
+      </c>
       <c r="G783">
         <v>140</v>
       </c>
@@ -17103,6 +18315,9 @@
       <c r="D784" t="s">
         <v>13</v>
       </c>
+      <c r="F784">
+        <v>657</v>
+      </c>
       <c r="G784">
         <v>122</v>
       </c>
@@ -17123,11 +18338,14 @@
       <c r="D785" t="s">
         <v>13</v>
       </c>
+      <c r="F785">
+        <v>657</v>
+      </c>
       <c r="G785">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H785">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="786" spans="1:8">
@@ -17143,6 +18361,9 @@
       <c r="D786" t="s">
         <v>14</v>
       </c>
+      <c r="F786">
+        <v>17</v>
+      </c>
     </row>
     <row r="787" spans="1:8">
       <c r="A787">
@@ -17157,6 +18378,9 @@
       <c r="D787" t="s">
         <v>14</v>
       </c>
+      <c r="F787">
+        <v>46</v>
+      </c>
     </row>
     <row r="788" spans="1:8">
       <c r="A788">
@@ -17171,6 +18395,9 @@
       <c r="D788" t="s">
         <v>14</v>
       </c>
+      <c r="F788">
+        <v>55</v>
+      </c>
     </row>
     <row r="789" spans="1:8">
       <c r="A789">
@@ -17185,6 +18412,9 @@
       <c r="D789" t="s">
         <v>14</v>
       </c>
+      <c r="F789">
+        <v>56</v>
+      </c>
     </row>
     <row r="790" spans="1:8">
       <c r="A790">
@@ -17199,6 +18429,9 @@
       <c r="D790" t="s">
         <v>14</v>
       </c>
+      <c r="F790">
+        <v>49</v>
+      </c>
     </row>
     <row r="791" spans="1:8">
       <c r="A791">
@@ -17213,6 +18446,9 @@
       <c r="D791" t="s">
         <v>14</v>
       </c>
+      <c r="F791">
+        <v>47</v>
+      </c>
     </row>
     <row r="792" spans="1:8">
       <c r="A792">
@@ -17227,6 +18463,9 @@
       <c r="D792" t="s">
         <v>14</v>
       </c>
+      <c r="F792">
+        <v>66</v>
+      </c>
     </row>
     <row r="793" spans="1:8">
       <c r="A793">
@@ -17241,6 +18480,9 @@
       <c r="D793" t="s">
         <v>14</v>
       </c>
+      <c r="F793">
+        <v>62</v>
+      </c>
       <c r="G793">
         <v>18</v>
       </c>
@@ -17261,6 +18503,9 @@
       <c r="D794" t="s">
         <v>14</v>
       </c>
+      <c r="F794">
+        <v>70</v>
+      </c>
       <c r="G794">
         <v>17</v>
       </c>
@@ -17281,11 +18526,14 @@
       <c r="D795" t="s">
         <v>14</v>
       </c>
+      <c r="F795">
+        <v>57</v>
+      </c>
       <c r="G795">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H795">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="796" spans="1:8">
@@ -17301,6 +18549,9 @@
       <c r="D796" t="s">
         <v>14</v>
       </c>
+      <c r="F796">
+        <v>67</v>
+      </c>
       <c r="G796">
         <v>22</v>
       </c>
@@ -17321,6 +18572,9 @@
       <c r="D797" t="s">
         <v>14</v>
       </c>
+      <c r="F797">
+        <v>58</v>
+      </c>
       <c r="G797">
         <v>21</v>
       </c>
@@ -17341,11 +18595,14 @@
       <c r="D798" t="s">
         <v>14</v>
       </c>
+      <c r="F798">
+        <v>99</v>
+      </c>
       <c r="G798">
         <v>21</v>
       </c>
       <c r="H798">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="799" spans="1:8">
@@ -17361,6 +18618,9 @@
       <c r="D799" t="s">
         <v>14</v>
       </c>
+      <c r="F799">
+        <v>98</v>
+      </c>
       <c r="G799">
         <v>22</v>
       </c>
@@ -17381,6 +18641,9 @@
       <c r="D800" t="s">
         <v>15</v>
       </c>
+      <c r="F800">
+        <v>7</v>
+      </c>
     </row>
     <row r="801" spans="1:8">
       <c r="A801">
@@ -17395,6 +18658,9 @@
       <c r="D801" t="s">
         <v>15</v>
       </c>
+      <c r="F801">
+        <v>22</v>
+      </c>
     </row>
     <row r="802" spans="1:8">
       <c r="A802">
@@ -17409,6 +18675,9 @@
       <c r="D802" t="s">
         <v>15</v>
       </c>
+      <c r="F802">
+        <v>13</v>
+      </c>
     </row>
     <row r="803" spans="1:8">
       <c r="A803">
@@ -17423,6 +18692,9 @@
       <c r="D803" t="s">
         <v>15</v>
       </c>
+      <c r="F803">
+        <v>28</v>
+      </c>
     </row>
     <row r="804" spans="1:8">
       <c r="A804">
@@ -17437,6 +18709,9 @@
       <c r="D804" t="s">
         <v>15</v>
       </c>
+      <c r="F804">
+        <v>10</v>
+      </c>
     </row>
     <row r="805" spans="1:8">
       <c r="A805">
@@ -17451,6 +18726,9 @@
       <c r="D805" t="s">
         <v>15</v>
       </c>
+      <c r="F805">
+        <v>17</v>
+      </c>
     </row>
     <row r="806" spans="1:8">
       <c r="A806">
@@ -17465,6 +18743,9 @@
       <c r="D806" t="s">
         <v>15</v>
       </c>
+      <c r="F806">
+        <v>12</v>
+      </c>
     </row>
     <row r="807" spans="1:8">
       <c r="A807">
@@ -17479,11 +18760,14 @@
       <c r="D807" t="s">
         <v>15</v>
       </c>
+      <c r="F807">
+        <v>17</v>
+      </c>
       <c r="G807">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H807">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="808" spans="1:8">
@@ -17499,6 +18783,9 @@
       <c r="D808" t="s">
         <v>15</v>
       </c>
+      <c r="F808">
+        <v>12</v>
+      </c>
       <c r="G808">
         <v>14</v>
       </c>
@@ -17519,6 +18806,9 @@
       <c r="D809" t="s">
         <v>15</v>
       </c>
+      <c r="F809">
+        <v>17</v>
+      </c>
       <c r="G809">
         <v>18</v>
       </c>
@@ -17539,6 +18829,9 @@
       <c r="D810" t="s">
         <v>15</v>
       </c>
+      <c r="F810">
+        <v>23</v>
+      </c>
       <c r="G810">
         <v>16</v>
       </c>
@@ -17559,6 +18852,9 @@
       <c r="D811" t="s">
         <v>15</v>
       </c>
+      <c r="F811">
+        <v>22</v>
+      </c>
       <c r="G811">
         <v>6</v>
       </c>
@@ -17579,6 +18875,9 @@
       <c r="D812" t="s">
         <v>15</v>
       </c>
+      <c r="F812">
+        <v>21</v>
+      </c>
       <c r="G812">
         <v>14</v>
       </c>
@@ -17599,6 +18898,9 @@
       <c r="D813" t="s">
         <v>15</v>
       </c>
+      <c r="F813">
+        <v>21</v>
+      </c>
       <c r="G813">
         <v>11</v>
       </c>
@@ -17619,6 +18921,9 @@
       <c r="D814" t="s">
         <v>16</v>
       </c>
+      <c r="F814">
+        <v>11</v>
+      </c>
     </row>
     <row r="815" spans="1:8">
       <c r="A815">
@@ -17633,6 +18938,9 @@
       <c r="D815" t="s">
         <v>16</v>
       </c>
+      <c r="F815">
+        <v>32</v>
+      </c>
     </row>
     <row r="816" spans="1:8">
       <c r="A816">
@@ -17647,6 +18955,9 @@
       <c r="D816" t="s">
         <v>16</v>
       </c>
+      <c r="F816">
+        <v>41</v>
+      </c>
     </row>
     <row r="817" spans="1:8">
       <c r="A817">
@@ -17661,6 +18972,9 @@
       <c r="D817" t="s">
         <v>16</v>
       </c>
+      <c r="F817">
+        <v>45</v>
+      </c>
     </row>
     <row r="818" spans="1:8">
       <c r="A818">
@@ -17675,6 +18989,9 @@
       <c r="D818" t="s">
         <v>16</v>
       </c>
+      <c r="F818">
+        <v>42</v>
+      </c>
     </row>
     <row r="819" spans="1:8">
       <c r="A819">
@@ -17689,6 +19006,9 @@
       <c r="D819" t="s">
         <v>16</v>
       </c>
+      <c r="F819">
+        <v>69</v>
+      </c>
     </row>
     <row r="820" spans="1:8">
       <c r="A820">
@@ -17703,6 +19023,9 @@
       <c r="D820" t="s">
         <v>16</v>
       </c>
+      <c r="F820">
+        <v>53</v>
+      </c>
     </row>
     <row r="821" spans="1:8">
       <c r="A821">
@@ -17717,11 +19040,14 @@
       <c r="D821" t="s">
         <v>16</v>
       </c>
+      <c r="F821">
+        <v>56</v>
+      </c>
       <c r="G821">
         <v>13</v>
       </c>
       <c r="H821">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="822" spans="1:8">
@@ -17737,11 +19063,14 @@
       <c r="D822" t="s">
         <v>16</v>
       </c>
+      <c r="F822">
+        <v>76</v>
+      </c>
       <c r="G822">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H822">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="823" spans="1:8">
@@ -17757,6 +19086,9 @@
       <c r="D823" t="s">
         <v>16</v>
       </c>
+      <c r="F823">
+        <v>86</v>
+      </c>
       <c r="G823">
         <v>28</v>
       </c>
@@ -17777,6 +19109,9 @@
       <c r="D824" t="s">
         <v>16</v>
       </c>
+      <c r="F824">
+        <v>74</v>
+      </c>
       <c r="G824">
         <v>31</v>
       </c>
@@ -17797,6 +19132,9 @@
       <c r="D825" t="s">
         <v>16</v>
       </c>
+      <c r="F825">
+        <v>86</v>
+      </c>
       <c r="G825">
         <v>36</v>
       </c>
@@ -17817,6 +19155,9 @@
       <c r="D826" t="s">
         <v>16</v>
       </c>
+      <c r="F826">
+        <v>95</v>
+      </c>
       <c r="G826">
         <v>22</v>
       </c>
@@ -17837,6 +19178,9 @@
       <c r="D827" t="s">
         <v>16</v>
       </c>
+      <c r="F827">
+        <v>89</v>
+      </c>
       <c r="G827">
         <v>32</v>
       </c>
@@ -17857,6 +19201,9 @@
       <c r="D828" t="s">
         <v>17</v>
       </c>
+      <c r="F828">
+        <v>0</v>
+      </c>
     </row>
     <row r="829" spans="1:8">
       <c r="A829">
@@ -17871,6 +19218,9 @@
       <c r="D829" t="s">
         <v>17</v>
       </c>
+      <c r="F829">
+        <v>1</v>
+      </c>
     </row>
     <row r="830" spans="1:8">
       <c r="A830">
@@ -17885,6 +19235,9 @@
       <c r="D830" t="s">
         <v>17</v>
       </c>
+      <c r="F830">
+        <v>1</v>
+      </c>
     </row>
     <row r="831" spans="1:8">
       <c r="A831">
@@ -17899,6 +19252,9 @@
       <c r="D831" t="s">
         <v>17</v>
       </c>
+      <c r="F831">
+        <v>1</v>
+      </c>
     </row>
     <row r="832" spans="1:8">
       <c r="A832">
@@ -17913,6 +19269,9 @@
       <c r="D832" t="s">
         <v>17</v>
       </c>
+      <c r="F832">
+        <v>1</v>
+      </c>
     </row>
     <row r="833" spans="1:8">
       <c r="A833">
@@ -17927,6 +19286,9 @@
       <c r="D833" t="s">
         <v>17</v>
       </c>
+      <c r="F833">
+        <v>0</v>
+      </c>
     </row>
     <row r="834" spans="1:8">
       <c r="A834">
@@ -17941,6 +19303,9 @@
       <c r="D834" t="s">
         <v>17</v>
       </c>
+      <c r="F834">
+        <v>1</v>
+      </c>
     </row>
     <row r="835" spans="1:8">
       <c r="A835">
@@ -17955,6 +19320,9 @@
       <c r="D835" t="s">
         <v>17</v>
       </c>
+      <c r="F835">
+        <v>2</v>
+      </c>
       <c r="G835">
         <v>0</v>
       </c>
@@ -17975,6 +19343,9 @@
       <c r="D836" t="s">
         <v>17</v>
       </c>
+      <c r="F836">
+        <v>1</v>
+      </c>
       <c r="G836">
         <v>2</v>
       </c>
@@ -17995,6 +19366,9 @@
       <c r="D837" t="s">
         <v>17</v>
       </c>
+      <c r="F837">
+        <v>1</v>
+      </c>
       <c r="G837">
         <v>1</v>
       </c>
@@ -18015,6 +19389,9 @@
       <c r="D838" t="s">
         <v>17</v>
       </c>
+      <c r="F838">
+        <v>0</v>
+      </c>
       <c r="G838">
         <v>0</v>
       </c>
@@ -18035,6 +19412,9 @@
       <c r="D839" t="s">
         <v>17</v>
       </c>
+      <c r="F839">
+        <v>1</v>
+      </c>
       <c r="G839">
         <v>0</v>
       </c>
@@ -18055,6 +19435,9 @@
       <c r="D840" t="s">
         <v>17</v>
       </c>
+      <c r="F840">
+        <v>1</v>
+      </c>
       <c r="G840">
         <v>1</v>
       </c>
@@ -18075,6 +19458,9 @@
       <c r="D841" t="s">
         <v>17</v>
       </c>
+      <c r="F841">
+        <v>0</v>
+      </c>
       <c r="G841">
         <v>0</v>
       </c>
@@ -18095,6 +19481,9 @@
       <c r="D842" t="s">
         <v>18</v>
       </c>
+      <c r="F842">
+        <v>3</v>
+      </c>
     </row>
     <row r="843" spans="1:8">
       <c r="A843">
@@ -18109,6 +19498,9 @@
       <c r="D843" t="s">
         <v>18</v>
       </c>
+      <c r="F843">
+        <v>5</v>
+      </c>
     </row>
     <row r="844" spans="1:8">
       <c r="A844">
@@ -18123,6 +19515,9 @@
       <c r="D844" t="s">
         <v>18</v>
       </c>
+      <c r="F844">
+        <v>14</v>
+      </c>
     </row>
     <row r="845" spans="1:8">
       <c r="A845">
@@ -18137,6 +19532,9 @@
       <c r="D845" t="s">
         <v>18</v>
       </c>
+      <c r="F845">
+        <v>33</v>
+      </c>
     </row>
     <row r="846" spans="1:8">
       <c r="A846">
@@ -18151,6 +19549,9 @@
       <c r="D846" t="s">
         <v>18</v>
       </c>
+      <c r="F846">
+        <v>19</v>
+      </c>
     </row>
     <row r="847" spans="1:8">
       <c r="A847">
@@ -18165,6 +19566,9 @@
       <c r="D847" t="s">
         <v>18</v>
       </c>
+      <c r="F847">
+        <v>17</v>
+      </c>
     </row>
     <row r="848" spans="1:8">
       <c r="A848">
@@ -18179,6 +19583,9 @@
       <c r="D848" t="s">
         <v>18</v>
       </c>
+      <c r="F848">
+        <v>26</v>
+      </c>
     </row>
     <row r="849" spans="1:8">
       <c r="A849">
@@ -18193,6 +19600,9 @@
       <c r="D849" t="s">
         <v>18</v>
       </c>
+      <c r="F849">
+        <v>32</v>
+      </c>
       <c r="G849">
         <v>8</v>
       </c>
@@ -18213,6 +19623,9 @@
       <c r="D850" t="s">
         <v>18</v>
       </c>
+      <c r="F850">
+        <v>35</v>
+      </c>
       <c r="G850">
         <v>15</v>
       </c>
@@ -18233,6 +19646,9 @@
       <c r="D851" t="s">
         <v>18</v>
       </c>
+      <c r="F851">
+        <v>28</v>
+      </c>
       <c r="G851">
         <v>10</v>
       </c>
@@ -18253,11 +19669,14 @@
       <c r="D852" t="s">
         <v>18</v>
       </c>
+      <c r="F852">
+        <v>39</v>
+      </c>
       <c r="G852">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H852">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="853" spans="1:8">
@@ -18273,6 +19692,9 @@
       <c r="D853" t="s">
         <v>18</v>
       </c>
+      <c r="F853">
+        <v>37</v>
+      </c>
       <c r="G853">
         <v>5</v>
       </c>
@@ -18293,6 +19715,9 @@
       <c r="D854" t="s">
         <v>18</v>
       </c>
+      <c r="F854">
+        <v>31</v>
+      </c>
       <c r="G854">
         <v>11</v>
       </c>
@@ -18313,6 +19738,9 @@
       <c r="D855" t="s">
         <v>18</v>
       </c>
+      <c r="F855">
+        <v>45</v>
+      </c>
       <c r="G855">
         <v>11</v>
       </c>
@@ -18333,6 +19761,9 @@
       <c r="D856" t="s">
         <v>19</v>
       </c>
+      <c r="F856">
+        <v>97</v>
+      </c>
     </row>
     <row r="857" spans="1:8">
       <c r="A857">
@@ -18347,6 +19778,9 @@
       <c r="D857" t="s">
         <v>19</v>
       </c>
+      <c r="F857">
+        <v>73</v>
+      </c>
     </row>
     <row r="858" spans="1:8">
       <c r="A858">
@@ -18361,6 +19795,9 @@
       <c r="D858" t="s">
         <v>19</v>
       </c>
+      <c r="F858">
+        <v>74</v>
+      </c>
     </row>
     <row r="859" spans="1:8">
       <c r="A859">
@@ -18375,6 +19812,9 @@
       <c r="D859" t="s">
         <v>19</v>
       </c>
+      <c r="F859">
+        <v>64</v>
+      </c>
     </row>
     <row r="860" spans="1:8">
       <c r="A860">
@@ -18389,6 +19829,9 @@
       <c r="D860" t="s">
         <v>19</v>
       </c>
+      <c r="F860">
+        <v>60</v>
+      </c>
     </row>
     <row r="861" spans="1:8">
       <c r="A861">
@@ -18403,6 +19846,9 @@
       <c r="D861" t="s">
         <v>19</v>
       </c>
+      <c r="F861">
+        <v>63</v>
+      </c>
     </row>
     <row r="862" spans="1:8">
       <c r="A862">
@@ -18417,6 +19863,9 @@
       <c r="D862" t="s">
         <v>19</v>
       </c>
+      <c r="F862">
+        <v>48</v>
+      </c>
     </row>
     <row r="863" spans="1:8">
       <c r="A863">
@@ -18431,11 +19880,14 @@
       <c r="D863" t="s">
         <v>19</v>
       </c>
+      <c r="F863">
+        <v>35</v>
+      </c>
       <c r="G863">
         <v>12</v>
       </c>
       <c r="H863">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="864" spans="1:8">
@@ -18451,6 +19903,9 @@
       <c r="D864" t="s">
         <v>19</v>
       </c>
+      <c r="F864">
+        <v>46</v>
+      </c>
       <c r="G864">
         <v>6</v>
       </c>
@@ -18471,6 +19926,9 @@
       <c r="D865" t="s">
         <v>19</v>
       </c>
+      <c r="F865">
+        <v>35</v>
+      </c>
       <c r="G865">
         <v>3</v>
       </c>
@@ -18491,6 +19949,9 @@
       <c r="D866" t="s">
         <v>19</v>
       </c>
+      <c r="F866">
+        <v>35</v>
+      </c>
       <c r="G866">
         <v>4</v>
       </c>
@@ -18511,6 +19972,9 @@
       <c r="D867" t="s">
         <v>19</v>
       </c>
+      <c r="F867">
+        <v>28</v>
+      </c>
       <c r="G867">
         <v>22</v>
       </c>
@@ -18531,6 +19995,9 @@
       <c r="D868" t="s">
         <v>19</v>
       </c>
+      <c r="F868">
+        <v>31</v>
+      </c>
       <c r="G868">
         <v>11</v>
       </c>
@@ -18551,6 +20018,9 @@
       <c r="D869" t="s">
         <v>19</v>
       </c>
+      <c r="F869">
+        <v>39</v>
+      </c>
       <c r="G869">
         <v>9</v>
       </c>
@@ -18571,6 +20041,9 @@
       <c r="D870" t="s">
         <v>20</v>
       </c>
+      <c r="F870">
+        <v>486</v>
+      </c>
     </row>
     <row r="871" spans="1:8">
       <c r="A871">
@@ -18585,6 +20058,9 @@
       <c r="D871" t="s">
         <v>20</v>
       </c>
+      <c r="F871">
+        <v>471</v>
+      </c>
     </row>
     <row r="872" spans="1:8">
       <c r="A872">
@@ -18599,6 +20075,9 @@
       <c r="D872" t="s">
         <v>20</v>
       </c>
+      <c r="F872">
+        <v>569</v>
+      </c>
     </row>
     <row r="873" spans="1:8">
       <c r="A873">
@@ -18613,6 +20092,9 @@
       <c r="D873" t="s">
         <v>20</v>
       </c>
+      <c r="F873">
+        <v>503</v>
+      </c>
     </row>
     <row r="874" spans="1:8">
       <c r="A874">
@@ -18627,6 +20109,9 @@
       <c r="D874" t="s">
         <v>20</v>
       </c>
+      <c r="F874">
+        <v>481</v>
+      </c>
     </row>
     <row r="875" spans="1:8">
       <c r="A875">
@@ -18641,6 +20126,9 @@
       <c r="D875" t="s">
         <v>20</v>
       </c>
+      <c r="F875">
+        <v>551</v>
+      </c>
     </row>
     <row r="876" spans="1:8">
       <c r="A876">
@@ -18655,6 +20143,9 @@
       <c r="D876" t="s">
         <v>20</v>
       </c>
+      <c r="F876">
+        <v>493</v>
+      </c>
     </row>
     <row r="877" spans="1:8">
       <c r="A877">
@@ -18669,11 +20160,14 @@
       <c r="D877" t="s">
         <v>20</v>
       </c>
+      <c r="F877">
+        <v>542</v>
+      </c>
       <c r="G877">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H877">
-        <v>353</v>
+        <v>360</v>
       </c>
     </row>
     <row r="878" spans="1:8">
@@ -18689,11 +20183,14 @@
       <c r="D878" t="s">
         <v>20</v>
       </c>
+      <c r="F878">
+        <v>606</v>
+      </c>
       <c r="G878">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H878">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="879" spans="1:8">
@@ -18709,11 +20206,14 @@
       <c r="D879" t="s">
         <v>20</v>
       </c>
+      <c r="F879">
+        <v>504</v>
+      </c>
       <c r="G879">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H879">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="880" spans="1:8">
@@ -18729,6 +20229,9 @@
       <c r="D880" t="s">
         <v>20</v>
       </c>
+      <c r="F880">
+        <v>582</v>
+      </c>
       <c r="G880">
         <v>83</v>
       </c>
@@ -18749,6 +20252,9 @@
       <c r="D881" t="s">
         <v>20</v>
       </c>
+      <c r="F881">
+        <v>574</v>
+      </c>
       <c r="G881">
         <v>164</v>
       </c>
@@ -18769,6 +20275,9 @@
       <c r="D882" t="s">
         <v>20</v>
       </c>
+      <c r="F882">
+        <v>494</v>
+      </c>
       <c r="G882">
         <v>158</v>
       </c>
@@ -18789,6 +20298,9 @@
       <c r="D883" t="s">
         <v>20</v>
       </c>
+      <c r="F883">
+        <v>529</v>
+      </c>
       <c r="G883">
         <v>145</v>
       </c>
@@ -18809,6 +20321,9 @@
       <c r="D884" t="s">
         <v>13</v>
       </c>
+      <c r="F884">
+        <v>209</v>
+      </c>
     </row>
     <row r="885" spans="1:8">
       <c r="A885">
@@ -18823,6 +20338,9 @@
       <c r="D885" t="s">
         <v>13</v>
       </c>
+      <c r="F885">
+        <v>526</v>
+      </c>
     </row>
     <row r="886" spans="1:8">
       <c r="A886">
@@ -18837,6 +20355,9 @@
       <c r="D886" t="s">
         <v>13</v>
       </c>
+      <c r="F886">
+        <v>515</v>
+      </c>
     </row>
     <row r="887" spans="1:8">
       <c r="A887">
@@ -18851,6 +20372,9 @@
       <c r="D887" t="s">
         <v>13</v>
       </c>
+      <c r="F887">
+        <v>604</v>
+      </c>
     </row>
     <row r="888" spans="1:8">
       <c r="A888">
@@ -18865,6 +20389,9 @@
       <c r="D888" t="s">
         <v>13</v>
       </c>
+      <c r="F888">
+        <v>609</v>
+      </c>
     </row>
     <row r="889" spans="1:8">
       <c r="A889">
@@ -18879,6 +20406,9 @@
       <c r="D889" t="s">
         <v>13</v>
       </c>
+      <c r="F889">
+        <v>543</v>
+      </c>
     </row>
     <row r="890" spans="1:8">
       <c r="A890">
@@ -18893,6 +20423,9 @@
       <c r="D890" t="s">
         <v>13</v>
       </c>
+      <c r="F890">
+        <v>542</v>
+      </c>
     </row>
     <row r="891" spans="1:8">
       <c r="A891">
@@ -18907,11 +20440,14 @@
       <c r="D891" t="s">
         <v>13</v>
       </c>
+      <c r="F891">
+        <v>475</v>
+      </c>
       <c r="G891">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H891">
-        <v>262</v>
+        <v>275</v>
       </c>
     </row>
     <row r="892" spans="1:8">
@@ -18927,11 +20463,14 @@
       <c r="D892" t="s">
         <v>13</v>
       </c>
+      <c r="F892">
+        <v>599</v>
+      </c>
       <c r="G892">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="H892">
-        <v>218</v>
+        <v>234</v>
       </c>
     </row>
     <row r="893" spans="1:8">
@@ -18947,11 +20486,14 @@
       <c r="D893" t="s">
         <v>13</v>
       </c>
+      <c r="F893">
+        <v>525</v>
+      </c>
       <c r="G893">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H893">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="894" spans="1:8">
@@ -18967,11 +20509,14 @@
       <c r="D894" t="s">
         <v>13</v>
       </c>
+      <c r="F894">
+        <v>523</v>
+      </c>
       <c r="G894">
         <v>133</v>
       </c>
       <c r="H894">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="895" spans="1:8">
@@ -18987,6 +20532,9 @@
       <c r="D895" t="s">
         <v>13</v>
       </c>
+      <c r="F895">
+        <v>449</v>
+      </c>
       <c r="G895">
         <v>105</v>
       </c>
@@ -19007,6 +20555,9 @@
       <c r="D896" t="s">
         <v>13</v>
       </c>
+      <c r="F896">
+        <v>507</v>
+      </c>
       <c r="G896">
         <v>90</v>
       </c>
@@ -19027,11 +20578,14 @@
       <c r="D897" t="s">
         <v>13</v>
       </c>
+      <c r="F897">
+        <v>495</v>
+      </c>
       <c r="G897">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H897">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="898" spans="1:8">
@@ -19047,6 +20601,9 @@
       <c r="D898" t="s">
         <v>14</v>
       </c>
+      <c r="F898">
+        <v>13</v>
+      </c>
     </row>
     <row r="899" spans="1:8">
       <c r="A899">
@@ -19061,6 +20618,9 @@
       <c r="D899" t="s">
         <v>14</v>
       </c>
+      <c r="F899">
+        <v>35</v>
+      </c>
     </row>
     <row r="900" spans="1:8">
       <c r="A900">
@@ -19075,6 +20635,9 @@
       <c r="D900" t="s">
         <v>14</v>
       </c>
+      <c r="F900">
+        <v>41</v>
+      </c>
     </row>
     <row r="901" spans="1:8">
       <c r="A901">
@@ -19089,6 +20652,9 @@
       <c r="D901" t="s">
         <v>14</v>
       </c>
+      <c r="F901">
+        <v>49</v>
+      </c>
     </row>
     <row r="902" spans="1:8">
       <c r="A902">
@@ -19103,6 +20669,9 @@
       <c r="D902" t="s">
         <v>14</v>
       </c>
+      <c r="F902">
+        <v>37</v>
+      </c>
     </row>
     <row r="903" spans="1:8">
       <c r="A903">
@@ -19117,6 +20686,9 @@
       <c r="D903" t="s">
         <v>14</v>
       </c>
+      <c r="F903">
+        <v>35</v>
+      </c>
     </row>
     <row r="904" spans="1:8">
       <c r="A904">
@@ -19131,6 +20703,9 @@
       <c r="D904" t="s">
         <v>14</v>
       </c>
+      <c r="F904">
+        <v>51</v>
+      </c>
     </row>
     <row r="905" spans="1:8">
       <c r="A905">
@@ -19145,6 +20720,9 @@
       <c r="D905" t="s">
         <v>14</v>
       </c>
+      <c r="F905">
+        <v>45</v>
+      </c>
       <c r="G905">
         <v>15</v>
       </c>
@@ -19165,6 +20743,9 @@
       <c r="D906" t="s">
         <v>14</v>
       </c>
+      <c r="F906">
+        <v>48</v>
+      </c>
       <c r="G906">
         <v>13</v>
       </c>
@@ -19185,11 +20766,14 @@
       <c r="D907" t="s">
         <v>14</v>
       </c>
+      <c r="F907">
+        <v>45</v>
+      </c>
       <c r="G907">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H907">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="908" spans="1:8">
@@ -19205,6 +20789,9 @@
       <c r="D908" t="s">
         <v>14</v>
       </c>
+      <c r="F908">
+        <v>50</v>
+      </c>
       <c r="G908">
         <v>15</v>
       </c>
@@ -19225,6 +20812,9 @@
       <c r="D909" t="s">
         <v>14</v>
       </c>
+      <c r="F909">
+        <v>44</v>
+      </c>
       <c r="G909">
         <v>16</v>
       </c>
@@ -19245,11 +20835,14 @@
       <c r="D910" t="s">
         <v>14</v>
       </c>
+      <c r="F910">
+        <v>70</v>
+      </c>
       <c r="G910">
         <v>16</v>
       </c>
       <c r="H910">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="911" spans="1:8">
@@ -19265,6 +20858,9 @@
       <c r="D911" t="s">
         <v>14</v>
       </c>
+      <c r="F911">
+        <v>74</v>
+      </c>
       <c r="G911">
         <v>17</v>
       </c>
@@ -19285,6 +20881,9 @@
       <c r="D912" t="s">
         <v>15</v>
       </c>
+      <c r="F912">
+        <v>5</v>
+      </c>
     </row>
     <row r="913" spans="1:8">
       <c r="A913">
@@ -19299,6 +20898,9 @@
       <c r="D913" t="s">
         <v>15</v>
       </c>
+      <c r="F913">
+        <v>19</v>
+      </c>
     </row>
     <row r="914" spans="1:8">
       <c r="A914">
@@ -19313,6 +20915,9 @@
       <c r="D914" t="s">
         <v>15</v>
       </c>
+      <c r="F914">
+        <v>11</v>
+      </c>
     </row>
     <row r="915" spans="1:8">
       <c r="A915">
@@ -19327,6 +20932,9 @@
       <c r="D915" t="s">
         <v>15</v>
       </c>
+      <c r="F915">
+        <v>22</v>
+      </c>
     </row>
     <row r="916" spans="1:8">
       <c r="A916">
@@ -19341,6 +20949,9 @@
       <c r="D916" t="s">
         <v>15</v>
       </c>
+      <c r="F916">
+        <v>9</v>
+      </c>
     </row>
     <row r="917" spans="1:8">
       <c r="A917">
@@ -19355,6 +20966,9 @@
       <c r="D917" t="s">
         <v>15</v>
       </c>
+      <c r="F917">
+        <v>14</v>
+      </c>
     </row>
     <row r="918" spans="1:8">
       <c r="A918">
@@ -19369,6 +20983,9 @@
       <c r="D918" t="s">
         <v>15</v>
       </c>
+      <c r="F918">
+        <v>11</v>
+      </c>
     </row>
     <row r="919" spans="1:8">
       <c r="A919">
@@ -19383,11 +21000,14 @@
       <c r="D919" t="s">
         <v>15</v>
       </c>
+      <c r="F919">
+        <v>12</v>
+      </c>
       <c r="G919">
         <v>6</v>
       </c>
       <c r="H919">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="920" spans="1:8">
@@ -19403,6 +21023,9 @@
       <c r="D920" t="s">
         <v>15</v>
       </c>
+      <c r="F920">
+        <v>10</v>
+      </c>
       <c r="G920">
         <v>10</v>
       </c>
@@ -19423,6 +21046,9 @@
       <c r="D921" t="s">
         <v>15</v>
       </c>
+      <c r="F921">
+        <v>14</v>
+      </c>
       <c r="G921">
         <v>17</v>
       </c>
@@ -19443,6 +21069,9 @@
       <c r="D922" t="s">
         <v>15</v>
       </c>
+      <c r="F922">
+        <v>17</v>
+      </c>
       <c r="G922">
         <v>13</v>
       </c>
@@ -19463,6 +21092,9 @@
       <c r="D923" t="s">
         <v>15</v>
       </c>
+      <c r="F923">
+        <v>19</v>
+      </c>
       <c r="G923">
         <v>4</v>
       </c>
@@ -19483,6 +21115,9 @@
       <c r="D924" t="s">
         <v>15</v>
       </c>
+      <c r="F924">
+        <v>16</v>
+      </c>
       <c r="G924">
         <v>8</v>
       </c>
@@ -19503,6 +21138,9 @@
       <c r="D925" t="s">
         <v>15</v>
       </c>
+      <c r="F925">
+        <v>17</v>
+      </c>
       <c r="G925">
         <v>9</v>
       </c>
@@ -19523,6 +21161,9 @@
       <c r="D926" t="s">
         <v>16</v>
       </c>
+      <c r="F926">
+        <v>7</v>
+      </c>
     </row>
     <row r="927" spans="1:8">
       <c r="A927">
@@ -19537,6 +21178,9 @@
       <c r="D927" t="s">
         <v>16</v>
       </c>
+      <c r="F927">
+        <v>29</v>
+      </c>
     </row>
     <row r="928" spans="1:8">
       <c r="A928">
@@ -19551,6 +21195,9 @@
       <c r="D928" t="s">
         <v>16</v>
       </c>
+      <c r="F928">
+        <v>34</v>
+      </c>
     </row>
     <row r="929" spans="1:8">
       <c r="A929">
@@ -19565,6 +21212,9 @@
       <c r="D929" t="s">
         <v>16</v>
       </c>
+      <c r="F929">
+        <v>40</v>
+      </c>
     </row>
     <row r="930" spans="1:8">
       <c r="A930">
@@ -19579,6 +21229,9 @@
       <c r="D930" t="s">
         <v>16</v>
       </c>
+      <c r="F930">
+        <v>37</v>
+      </c>
     </row>
     <row r="931" spans="1:8">
       <c r="A931">
@@ -19593,6 +21246,9 @@
       <c r="D931" t="s">
         <v>16</v>
       </c>
+      <c r="F931">
+        <v>59</v>
+      </c>
     </row>
     <row r="932" spans="1:8">
       <c r="A932">
@@ -19607,6 +21263,9 @@
       <c r="D932" t="s">
         <v>16</v>
       </c>
+      <c r="F932">
+        <v>45</v>
+      </c>
     </row>
     <row r="933" spans="1:8">
       <c r="A933">
@@ -19621,11 +21280,14 @@
       <c r="D933" t="s">
         <v>16</v>
       </c>
+      <c r="F933">
+        <v>45</v>
+      </c>
       <c r="G933">
         <v>12</v>
       </c>
       <c r="H933">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="934" spans="1:8">
@@ -19641,11 +21303,14 @@
       <c r="D934" t="s">
         <v>16</v>
       </c>
+      <c r="F934">
+        <v>63</v>
+      </c>
       <c r="G934">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H934">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="935" spans="1:8">
@@ -19661,6 +21326,9 @@
       <c r="D935" t="s">
         <v>16</v>
       </c>
+      <c r="F935">
+        <v>70</v>
+      </c>
       <c r="G935">
         <v>26</v>
       </c>
@@ -19681,6 +21349,9 @@
       <c r="D936" t="s">
         <v>16</v>
       </c>
+      <c r="F936">
+        <v>54</v>
+      </c>
       <c r="G936">
         <v>25</v>
       </c>
@@ -19701,6 +21372,9 @@
       <c r="D937" t="s">
         <v>16</v>
       </c>
+      <c r="F937">
+        <v>67</v>
+      </c>
       <c r="G937">
         <v>28</v>
       </c>
@@ -19721,6 +21395,9 @@
       <c r="D938" t="s">
         <v>16</v>
       </c>
+      <c r="F938">
+        <v>73</v>
+      </c>
       <c r="G938">
         <v>18</v>
       </c>
@@ -19741,6 +21418,9 @@
       <c r="D939" t="s">
         <v>16</v>
       </c>
+      <c r="F939">
+        <v>68</v>
+      </c>
       <c r="G939">
         <v>25</v>
       </c>
@@ -19761,6 +21441,9 @@
       <c r="D940" t="s">
         <v>17</v>
       </c>
+      <c r="F940">
+        <v>0</v>
+      </c>
     </row>
     <row r="941" spans="1:8">
       <c r="A941">
@@ -19775,6 +21458,9 @@
       <c r="D941" t="s">
         <v>17</v>
       </c>
+      <c r="F941">
+        <v>0</v>
+      </c>
     </row>
     <row r="942" spans="1:8">
       <c r="A942">
@@ -19789,6 +21475,9 @@
       <c r="D942" t="s">
         <v>17</v>
       </c>
+      <c r="F942">
+        <v>0</v>
+      </c>
     </row>
     <row r="943" spans="1:8">
       <c r="A943">
@@ -19803,6 +21492,9 @@
       <c r="D943" t="s">
         <v>17</v>
       </c>
+      <c r="F943">
+        <v>1</v>
+      </c>
     </row>
     <row r="944" spans="1:8">
       <c r="A944">
@@ -19817,6 +21509,9 @@
       <c r="D944" t="s">
         <v>17</v>
       </c>
+      <c r="F944">
+        <v>1</v>
+      </c>
     </row>
     <row r="945" spans="1:8">
       <c r="A945">
@@ -19831,6 +21526,9 @@
       <c r="D945" t="s">
         <v>17</v>
       </c>
+      <c r="F945">
+        <v>0</v>
+      </c>
     </row>
     <row r="946" spans="1:8">
       <c r="A946">
@@ -19845,6 +21543,9 @@
       <c r="D946" t="s">
         <v>17</v>
       </c>
+      <c r="F946">
+        <v>1</v>
+      </c>
     </row>
     <row r="947" spans="1:8">
       <c r="A947">
@@ -19859,6 +21560,9 @@
       <c r="D947" t="s">
         <v>17</v>
       </c>
+      <c r="F947">
+        <v>0</v>
+      </c>
       <c r="G947">
         <v>0</v>
       </c>
@@ -19879,6 +21583,9 @@
       <c r="D948" t="s">
         <v>17</v>
       </c>
+      <c r="F948">
+        <v>1</v>
+      </c>
       <c r="G948">
         <v>2</v>
       </c>
@@ -19899,6 +21606,9 @@
       <c r="D949" t="s">
         <v>17</v>
       </c>
+      <c r="F949">
+        <v>1</v>
+      </c>
       <c r="G949">
         <v>0</v>
       </c>
@@ -19919,6 +21629,9 @@
       <c r="D950" t="s">
         <v>17</v>
       </c>
+      <c r="F950">
+        <v>0</v>
+      </c>
       <c r="G950">
         <v>0</v>
       </c>
@@ -19939,6 +21652,9 @@
       <c r="D951" t="s">
         <v>17</v>
       </c>
+      <c r="F951">
+        <v>0</v>
+      </c>
       <c r="G951">
         <v>0</v>
       </c>
@@ -19959,6 +21675,9 @@
       <c r="D952" t="s">
         <v>17</v>
       </c>
+      <c r="F952">
+        <v>1</v>
+      </c>
       <c r="G952">
         <v>1</v>
       </c>
@@ -19979,6 +21698,9 @@
       <c r="D953" t="s">
         <v>17</v>
       </c>
+      <c r="F953">
+        <v>0</v>
+      </c>
       <c r="G953">
         <v>0</v>
       </c>
@@ -19999,6 +21721,9 @@
       <c r="D954" t="s">
         <v>18</v>
       </c>
+      <c r="F954">
+        <v>1</v>
+      </c>
     </row>
     <row r="955" spans="1:8">
       <c r="A955">
@@ -20013,6 +21738,9 @@
       <c r="D955" t="s">
         <v>18</v>
       </c>
+      <c r="F955">
+        <v>4</v>
+      </c>
     </row>
     <row r="956" spans="1:8">
       <c r="A956">
@@ -20027,6 +21755,9 @@
       <c r="D956" t="s">
         <v>18</v>
       </c>
+      <c r="F956">
+        <v>11</v>
+      </c>
     </row>
     <row r="957" spans="1:8">
       <c r="A957">
@@ -20041,6 +21772,9 @@
       <c r="D957" t="s">
         <v>18</v>
       </c>
+      <c r="F957">
+        <v>27</v>
+      </c>
     </row>
     <row r="958" spans="1:8">
       <c r="A958">
@@ -20055,6 +21789,9 @@
       <c r="D958" t="s">
         <v>18</v>
       </c>
+      <c r="F958">
+        <v>11</v>
+      </c>
     </row>
     <row r="959" spans="1:8">
       <c r="A959">
@@ -20069,6 +21806,9 @@
       <c r="D959" t="s">
         <v>18</v>
       </c>
+      <c r="F959">
+        <v>12</v>
+      </c>
     </row>
     <row r="960" spans="1:8">
       <c r="A960">
@@ -20083,6 +21823,9 @@
       <c r="D960" t="s">
         <v>18</v>
       </c>
+      <c r="F960">
+        <v>19</v>
+      </c>
     </row>
     <row r="961" spans="1:8">
       <c r="A961">
@@ -20097,6 +21840,9 @@
       <c r="D961" t="s">
         <v>18</v>
       </c>
+      <c r="F961">
+        <v>26</v>
+      </c>
       <c r="G961">
         <v>7</v>
       </c>
@@ -20117,6 +21863,9 @@
       <c r="D962" t="s">
         <v>18</v>
       </c>
+      <c r="F962">
+        <v>24</v>
+      </c>
       <c r="G962">
         <v>12</v>
       </c>
@@ -20137,6 +21886,9 @@
       <c r="D963" t="s">
         <v>18</v>
       </c>
+      <c r="F963">
+        <v>21</v>
+      </c>
       <c r="G963">
         <v>9</v>
       </c>
@@ -20157,11 +21909,14 @@
       <c r="D964" t="s">
         <v>18</v>
       </c>
+      <c r="F964">
+        <v>28</v>
+      </c>
       <c r="G964">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H964">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="965" spans="1:8">
@@ -20177,6 +21932,9 @@
       <c r="D965" t="s">
         <v>18</v>
       </c>
+      <c r="F965">
+        <v>27</v>
+      </c>
       <c r="G965">
         <v>4</v>
       </c>
@@ -20197,6 +21955,9 @@
       <c r="D966" t="s">
         <v>18</v>
       </c>
+      <c r="F966">
+        <v>24</v>
+      </c>
       <c r="G966">
         <v>7</v>
       </c>
@@ -20217,6 +21978,9 @@
       <c r="D967" t="s">
         <v>18</v>
       </c>
+      <c r="F967">
+        <v>29</v>
+      </c>
       <c r="G967">
         <v>11</v>
       </c>
@@ -20237,6 +22001,9 @@
       <c r="D968" t="s">
         <v>19</v>
       </c>
+      <c r="F968">
+        <v>82</v>
+      </c>
     </row>
     <row r="969" spans="1:8">
       <c r="A969">
@@ -20251,6 +22018,9 @@
       <c r="D969" t="s">
         <v>19</v>
       </c>
+      <c r="F969">
+        <v>54</v>
+      </c>
     </row>
     <row r="970" spans="1:8">
       <c r="A970">
@@ -20265,6 +22035,9 @@
       <c r="D970" t="s">
         <v>19</v>
       </c>
+      <c r="F970">
+        <v>63</v>
+      </c>
     </row>
     <row r="971" spans="1:8">
       <c r="A971">
@@ -20279,6 +22052,9 @@
       <c r="D971" t="s">
         <v>19</v>
       </c>
+      <c r="F971">
+        <v>51</v>
+      </c>
     </row>
     <row r="972" spans="1:8">
       <c r="A972">
@@ -20293,6 +22069,9 @@
       <c r="D972" t="s">
         <v>19</v>
       </c>
+      <c r="F972">
+        <v>47</v>
+      </c>
     </row>
     <row r="973" spans="1:8">
       <c r="A973">
@@ -20307,6 +22086,9 @@
       <c r="D973" t="s">
         <v>19</v>
       </c>
+      <c r="F973">
+        <v>57</v>
+      </c>
     </row>
     <row r="974" spans="1:8">
       <c r="A974">
@@ -20321,6 +22103,9 @@
       <c r="D974" t="s">
         <v>19</v>
       </c>
+      <c r="F974">
+        <v>38</v>
+      </c>
     </row>
     <row r="975" spans="1:8">
       <c r="A975">
@@ -20335,6 +22120,9 @@
       <c r="D975" t="s">
         <v>19</v>
       </c>
+      <c r="F975">
+        <v>29</v>
+      </c>
       <c r="G975">
         <v>11</v>
       </c>
@@ -20355,6 +22143,9 @@
       <c r="D976" t="s">
         <v>19</v>
       </c>
+      <c r="F976">
+        <v>34</v>
+      </c>
       <c r="G976">
         <v>6</v>
       </c>
@@ -20375,6 +22166,9 @@
       <c r="D977" t="s">
         <v>19</v>
       </c>
+      <c r="F977">
+        <v>27</v>
+      </c>
       <c r="G977">
         <v>3</v>
       </c>
@@ -20395,6 +22189,9 @@
       <c r="D978" t="s">
         <v>19</v>
       </c>
+      <c r="F978">
+        <v>23</v>
+      </c>
       <c r="G978">
         <v>4</v>
       </c>
@@ -20415,6 +22212,9 @@
       <c r="D979" t="s">
         <v>19</v>
       </c>
+      <c r="F979">
+        <v>20</v>
+      </c>
       <c r="G979">
         <v>20</v>
       </c>
@@ -20435,6 +22235,9 @@
       <c r="D980" t="s">
         <v>19</v>
       </c>
+      <c r="F980">
+        <v>29</v>
+      </c>
       <c r="G980">
         <v>10</v>
       </c>
@@ -20455,6 +22258,9 @@
       <c r="D981" t="s">
         <v>19</v>
       </c>
+      <c r="F981">
+        <v>32</v>
+      </c>
       <c r="G981">
         <v>8</v>
       </c>
@@ -20475,6 +22281,9 @@
       <c r="D982" t="s">
         <v>20</v>
       </c>
+      <c r="F982">
+        <v>368</v>
+      </c>
     </row>
     <row r="983" spans="1:8">
       <c r="A983">
@@ -20489,6 +22298,9 @@
       <c r="D983" t="s">
         <v>20</v>
       </c>
+      <c r="F983">
+        <v>345</v>
+      </c>
     </row>
     <row r="984" spans="1:8">
       <c r="A984">
@@ -20503,6 +22315,9 @@
       <c r="D984" t="s">
         <v>20</v>
       </c>
+      <c r="F984">
+        <v>453</v>
+      </c>
     </row>
     <row r="985" spans="1:8">
       <c r="A985">
@@ -20517,6 +22332,9 @@
       <c r="D985" t="s">
         <v>20</v>
       </c>
+      <c r="F985">
+        <v>395</v>
+      </c>
     </row>
     <row r="986" spans="1:8">
       <c r="A986">
@@ -20531,6 +22349,9 @@
       <c r="D986" t="s">
         <v>20</v>
       </c>
+      <c r="F986">
+        <v>342</v>
+      </c>
     </row>
     <row r="987" spans="1:8">
       <c r="A987">
@@ -20545,6 +22366,9 @@
       <c r="D987" t="s">
         <v>20</v>
       </c>
+      <c r="F987">
+        <v>396</v>
+      </c>
     </row>
     <row r="988" spans="1:8">
       <c r="A988">
@@ -20559,6 +22383,9 @@
       <c r="D988" t="s">
         <v>20</v>
       </c>
+      <c r="F988">
+        <v>371</v>
+      </c>
     </row>
     <row r="989" spans="1:8">
       <c r="A989">
@@ -20573,11 +22400,14 @@
       <c r="D989" t="s">
         <v>20</v>
       </c>
+      <c r="F989">
+        <v>399</v>
+      </c>
       <c r="G989">
         <v>103</v>
       </c>
       <c r="H989">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="990" spans="1:8">
@@ -20593,11 +22423,14 @@
       <c r="D990" t="s">
         <v>20</v>
       </c>
+      <c r="F990">
+        <v>436</v>
+      </c>
       <c r="G990">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H990">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="991" spans="1:8">
@@ -20613,11 +22446,14 @@
       <c r="D991" t="s">
         <v>20</v>
       </c>
+      <c r="F991">
+        <v>375</v>
+      </c>
       <c r="G991">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H991">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="992" spans="1:8">
@@ -20633,6 +22469,9 @@
       <c r="D992" t="s">
         <v>20</v>
       </c>
+      <c r="F992">
+        <v>446</v>
+      </c>
       <c r="G992">
         <v>65</v>
       </c>
@@ -20653,6 +22492,9 @@
       <c r="D993" t="s">
         <v>20</v>
       </c>
+      <c r="F993">
+        <v>441</v>
+      </c>
       <c r="G993">
         <v>116</v>
       </c>
@@ -20673,6 +22515,9 @@
       <c r="D994" t="s">
         <v>20</v>
       </c>
+      <c r="F994">
+        <v>378</v>
+      </c>
       <c r="G994">
         <v>108</v>
       </c>
@@ -20693,6 +22538,9 @@
       <c r="D995" t="s">
         <v>20</v>
       </c>
+      <c r="F995">
+        <v>404</v>
+      </c>
       <c r="G995">
         <v>96</v>
       </c>
@@ -20713,6 +22561,9 @@
       <c r="D996" t="s">
         <v>13</v>
       </c>
+      <c r="F996">
+        <v>49</v>
+      </c>
     </row>
     <row r="997" spans="1:8">
       <c r="A997">
@@ -20727,6 +22578,9 @@
       <c r="D997" t="s">
         <v>13</v>
       </c>
+      <c r="F997">
+        <v>129</v>
+      </c>
     </row>
     <row r="998" spans="1:8">
       <c r="A998">
@@ -20741,6 +22595,9 @@
       <c r="D998" t="s">
         <v>13</v>
       </c>
+      <c r="F998">
+        <v>154</v>
+      </c>
     </row>
     <row r="999" spans="1:8">
       <c r="A999">
@@ -20755,6 +22612,9 @@
       <c r="D999" t="s">
         <v>13</v>
       </c>
+      <c r="F999">
+        <v>139</v>
+      </c>
     </row>
     <row r="1000" spans="1:8">
       <c r="A1000">
@@ -20769,6 +22629,9 @@
       <c r="D1000" t="s">
         <v>13</v>
       </c>
+      <c r="F1000">
+        <v>140</v>
+      </c>
     </row>
     <row r="1001" spans="1:8">
       <c r="A1001">
@@ -20783,6 +22646,9 @@
       <c r="D1001" t="s">
         <v>13</v>
       </c>
+      <c r="F1001">
+        <v>122</v>
+      </c>
     </row>
     <row r="1002" spans="1:8">
       <c r="A1002">
@@ -20797,6 +22663,9 @@
       <c r="D1002" t="s">
         <v>13</v>
       </c>
+      <c r="F1002">
+        <v>131</v>
+      </c>
     </row>
     <row r="1003" spans="1:8">
       <c r="A1003">
@@ -20811,11 +22680,14 @@
       <c r="D1003" t="s">
         <v>13</v>
       </c>
+      <c r="F1003">
+        <v>131</v>
+      </c>
       <c r="G1003">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1003">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1004" spans="1:8">
@@ -20831,11 +22703,14 @@
       <c r="D1004" t="s">
         <v>13</v>
       </c>
+      <c r="F1004">
+        <v>139</v>
+      </c>
       <c r="G1004">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H1004">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1005" spans="1:8">
@@ -20851,6 +22726,9 @@
       <c r="D1005" t="s">
         <v>13</v>
       </c>
+      <c r="F1005">
+        <v>120</v>
+      </c>
       <c r="G1005">
         <v>19</v>
       </c>
@@ -20871,11 +22749,14 @@
       <c r="D1006" t="s">
         <v>13</v>
       </c>
+      <c r="F1006">
+        <v>131</v>
+      </c>
       <c r="G1006">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H1006">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="1007" spans="1:8">
@@ -20891,6 +22772,9 @@
       <c r="D1007" t="s">
         <v>13</v>
       </c>
+      <c r="F1007">
+        <v>127</v>
+      </c>
       <c r="G1007">
         <v>35</v>
       </c>
@@ -20911,6 +22795,9 @@
       <c r="D1008" t="s">
         <v>13</v>
       </c>
+      <c r="F1008">
+        <v>150</v>
+      </c>
       <c r="G1008">
         <v>32</v>
       </c>
@@ -20931,6 +22818,9 @@
       <c r="D1009" t="s">
         <v>13</v>
       </c>
+      <c r="F1009">
+        <v>162</v>
+      </c>
       <c r="G1009">
         <v>35</v>
       </c>
@@ -20951,6 +22841,9 @@
       <c r="D1010" t="s">
         <v>14</v>
       </c>
+      <c r="F1010">
+        <v>4</v>
+      </c>
     </row>
     <row r="1011" spans="1:8">
       <c r="A1011">
@@ -20965,6 +22858,9 @@
       <c r="D1011" t="s">
         <v>14</v>
       </c>
+      <c r="F1011">
+        <v>11</v>
+      </c>
     </row>
     <row r="1012" spans="1:8">
       <c r="A1012">
@@ -20979,6 +22875,9 @@
       <c r="D1012" t="s">
         <v>14</v>
       </c>
+      <c r="F1012">
+        <v>14</v>
+      </c>
     </row>
     <row r="1013" spans="1:8">
       <c r="A1013">
@@ -20993,6 +22892,9 @@
       <c r="D1013" t="s">
         <v>14</v>
       </c>
+      <c r="F1013">
+        <v>7</v>
+      </c>
     </row>
     <row r="1014" spans="1:8">
       <c r="A1014">
@@ -21007,6 +22909,9 @@
       <c r="D1014" t="s">
         <v>14</v>
       </c>
+      <c r="F1014">
+        <v>12</v>
+      </c>
     </row>
     <row r="1015" spans="1:8">
       <c r="A1015">
@@ -21021,6 +22926,9 @@
       <c r="D1015" t="s">
         <v>14</v>
       </c>
+      <c r="F1015">
+        <v>12</v>
+      </c>
     </row>
     <row r="1016" spans="1:8">
       <c r="A1016">
@@ -21035,6 +22943,9 @@
       <c r="D1016" t="s">
         <v>14</v>
       </c>
+      <c r="F1016">
+        <v>15</v>
+      </c>
     </row>
     <row r="1017" spans="1:8">
       <c r="A1017">
@@ -21049,6 +22960,9 @@
       <c r="D1017" t="s">
         <v>14</v>
       </c>
+      <c r="F1017">
+        <v>17</v>
+      </c>
       <c r="G1017">
         <v>3</v>
       </c>
@@ -21069,6 +22983,9 @@
       <c r="D1018" t="s">
         <v>14</v>
       </c>
+      <c r="F1018">
+        <v>22</v>
+      </c>
       <c r="G1018">
         <v>4</v>
       </c>
@@ -21089,6 +23006,9 @@
       <c r="D1019" t="s">
         <v>14</v>
       </c>
+      <c r="F1019">
+        <v>12</v>
+      </c>
       <c r="G1019">
         <v>6</v>
       </c>
@@ -21109,6 +23029,9 @@
       <c r="D1020" t="s">
         <v>14</v>
       </c>
+      <c r="F1020">
+        <v>17</v>
+      </c>
       <c r="G1020">
         <v>7</v>
       </c>
@@ -21129,6 +23052,9 @@
       <c r="D1021" t="s">
         <v>14</v>
       </c>
+      <c r="F1021">
+        <v>14</v>
+      </c>
       <c r="G1021">
         <v>5</v>
       </c>
@@ -21149,6 +23075,9 @@
       <c r="D1022" t="s">
         <v>14</v>
       </c>
+      <c r="F1022">
+        <v>29</v>
+      </c>
       <c r="G1022">
         <v>5</v>
       </c>
@@ -21169,6 +23098,9 @@
       <c r="D1023" t="s">
         <v>14</v>
       </c>
+      <c r="F1023">
+        <v>24</v>
+      </c>
       <c r="G1023">
         <v>5</v>
       </c>
@@ -21189,6 +23121,9 @@
       <c r="D1024" t="s">
         <v>15</v>
       </c>
+      <c r="F1024">
+        <v>2</v>
+      </c>
     </row>
     <row r="1025" spans="1:8">
       <c r="A1025">
@@ -21203,6 +23138,9 @@
       <c r="D1025" t="s">
         <v>15</v>
       </c>
+      <c r="F1025">
+        <v>3</v>
+      </c>
     </row>
     <row r="1026" spans="1:8">
       <c r="A1026">
@@ -21217,6 +23155,9 @@
       <c r="D1026" t="s">
         <v>15</v>
       </c>
+      <c r="F1026">
+        <v>2</v>
+      </c>
     </row>
     <row r="1027" spans="1:8">
       <c r="A1027">
@@ -21231,6 +23172,9 @@
       <c r="D1027" t="s">
         <v>15</v>
       </c>
+      <c r="F1027">
+        <v>6</v>
+      </c>
     </row>
     <row r="1028" spans="1:8">
       <c r="A1028">
@@ -21245,6 +23189,9 @@
       <c r="D1028" t="s">
         <v>15</v>
       </c>
+      <c r="F1028">
+        <v>1</v>
+      </c>
     </row>
     <row r="1029" spans="1:8">
       <c r="A1029">
@@ -21259,6 +23206,9 @@
       <c r="D1029" t="s">
         <v>15</v>
       </c>
+      <c r="F1029">
+        <v>3</v>
+      </c>
     </row>
     <row r="1030" spans="1:8">
       <c r="A1030">
@@ -21273,6 +23223,9 @@
       <c r="D1030" t="s">
         <v>15</v>
       </c>
+      <c r="F1030">
+        <v>1</v>
+      </c>
     </row>
     <row r="1031" spans="1:8">
       <c r="A1031">
@@ -21287,11 +23240,14 @@
       <c r="D1031" t="s">
         <v>15</v>
       </c>
+      <c r="F1031">
+        <v>5</v>
+      </c>
       <c r="G1031">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1031">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1032" spans="1:8">
@@ -21307,6 +23263,9 @@
       <c r="D1032" t="s">
         <v>15</v>
       </c>
+      <c r="F1032">
+        <v>2</v>
+      </c>
       <c r="G1032">
         <v>4</v>
       </c>
@@ -21327,6 +23286,9 @@
       <c r="D1033" t="s">
         <v>15</v>
       </c>
+      <c r="F1033">
+        <v>3</v>
+      </c>
       <c r="G1033">
         <v>1</v>
       </c>
@@ -21347,6 +23309,9 @@
       <c r="D1034" t="s">
         <v>15</v>
       </c>
+      <c r="F1034">
+        <v>6</v>
+      </c>
       <c r="G1034">
         <v>3</v>
       </c>
@@ -21367,6 +23332,9 @@
       <c r="D1035" t="s">
         <v>15</v>
       </c>
+      <c r="F1035">
+        <v>3</v>
+      </c>
       <c r="G1035">
         <v>2</v>
       </c>
@@ -21387,6 +23355,9 @@
       <c r="D1036" t="s">
         <v>15</v>
       </c>
+      <c r="F1036">
+        <v>5</v>
+      </c>
       <c r="G1036">
         <v>6</v>
       </c>
@@ -21407,6 +23378,9 @@
       <c r="D1037" t="s">
         <v>15</v>
       </c>
+      <c r="F1037">
+        <v>4</v>
+      </c>
       <c r="G1037">
         <v>2</v>
       </c>
@@ -21427,6 +23401,9 @@
       <c r="D1038" t="s">
         <v>16</v>
       </c>
+      <c r="F1038">
+        <v>4</v>
+      </c>
     </row>
     <row r="1039" spans="1:8">
       <c r="A1039">
@@ -21441,6 +23418,9 @@
       <c r="D1039" t="s">
         <v>16</v>
       </c>
+      <c r="F1039">
+        <v>3</v>
+      </c>
     </row>
     <row r="1040" spans="1:8">
       <c r="A1040">
@@ -21455,6 +23435,9 @@
       <c r="D1040" t="s">
         <v>16</v>
       </c>
+      <c r="F1040">
+        <v>7</v>
+      </c>
     </row>
     <row r="1041" spans="1:8">
       <c r="A1041">
@@ -21469,6 +23452,9 @@
       <c r="D1041" t="s">
         <v>16</v>
       </c>
+      <c r="F1041">
+        <v>5</v>
+      </c>
     </row>
     <row r="1042" spans="1:8">
       <c r="A1042">
@@ -21483,6 +23469,9 @@
       <c r="D1042" t="s">
         <v>16</v>
       </c>
+      <c r="F1042">
+        <v>5</v>
+      </c>
     </row>
     <row r="1043" spans="1:8">
       <c r="A1043">
@@ -21497,6 +23486,9 @@
       <c r="D1043" t="s">
         <v>16</v>
       </c>
+      <c r="F1043">
+        <v>10</v>
+      </c>
     </row>
     <row r="1044" spans="1:8">
       <c r="A1044">
@@ -21511,6 +23503,9 @@
       <c r="D1044" t="s">
         <v>16</v>
       </c>
+      <c r="F1044">
+        <v>8</v>
+      </c>
     </row>
     <row r="1045" spans="1:8">
       <c r="A1045">
@@ -21525,6 +23520,9 @@
       <c r="D1045" t="s">
         <v>16</v>
       </c>
+      <c r="F1045">
+        <v>11</v>
+      </c>
       <c r="G1045">
         <v>1</v>
       </c>
@@ -21545,6 +23543,9 @@
       <c r="D1046" t="s">
         <v>16</v>
       </c>
+      <c r="F1046">
+        <v>13</v>
+      </c>
       <c r="G1046">
         <v>9</v>
       </c>
@@ -21565,6 +23566,9 @@
       <c r="D1047" t="s">
         <v>16</v>
       </c>
+      <c r="F1047">
+        <v>16</v>
+      </c>
       <c r="G1047">
         <v>2</v>
       </c>
@@ -21585,6 +23589,9 @@
       <c r="D1048" t="s">
         <v>16</v>
       </c>
+      <c r="F1048">
+        <v>20</v>
+      </c>
       <c r="G1048">
         <v>6</v>
       </c>
@@ -21605,6 +23612,9 @@
       <c r="D1049" t="s">
         <v>16</v>
       </c>
+      <c r="F1049">
+        <v>19</v>
+      </c>
       <c r="G1049">
         <v>8</v>
       </c>
@@ -21625,6 +23635,9 @@
       <c r="D1050" t="s">
         <v>16</v>
       </c>
+      <c r="F1050">
+        <v>22</v>
+      </c>
       <c r="G1050">
         <v>4</v>
       </c>
@@ -21645,6 +23658,9 @@
       <c r="D1051" t="s">
         <v>16</v>
       </c>
+      <c r="F1051">
+        <v>21</v>
+      </c>
       <c r="G1051">
         <v>7</v>
       </c>
@@ -21665,6 +23681,9 @@
       <c r="D1052" t="s">
         <v>17</v>
       </c>
+      <c r="F1052">
+        <v>0</v>
+      </c>
     </row>
     <row r="1053" spans="1:8">
       <c r="A1053">
@@ -21679,6 +23698,9 @@
       <c r="D1053" t="s">
         <v>17</v>
       </c>
+      <c r="F1053">
+        <v>1</v>
+      </c>
     </row>
     <row r="1054" spans="1:8">
       <c r="A1054">
@@ -21693,6 +23715,9 @@
       <c r="D1054" t="s">
         <v>17</v>
       </c>
+      <c r="F1054">
+        <v>1</v>
+      </c>
     </row>
     <row r="1055" spans="1:8">
       <c r="A1055">
@@ -21707,6 +23732,9 @@
       <c r="D1055" t="s">
         <v>17</v>
       </c>
+      <c r="F1055">
+        <v>0</v>
+      </c>
     </row>
     <row r="1056" spans="1:8">
       <c r="A1056">
@@ -21721,6 +23749,9 @@
       <c r="D1056" t="s">
         <v>17</v>
       </c>
+      <c r="F1056">
+        <v>0</v>
+      </c>
     </row>
     <row r="1057" spans="1:8">
       <c r="A1057">
@@ -21735,6 +23766,9 @@
       <c r="D1057" t="s">
         <v>17</v>
       </c>
+      <c r="F1057">
+        <v>0</v>
+      </c>
     </row>
     <row r="1058" spans="1:8">
       <c r="A1058">
@@ -21749,6 +23783,9 @@
       <c r="D1058" t="s">
         <v>17</v>
       </c>
+      <c r="F1058">
+        <v>0</v>
+      </c>
     </row>
     <row r="1059" spans="1:8">
       <c r="A1059">
@@ -21763,6 +23800,9 @@
       <c r="D1059" t="s">
         <v>17</v>
       </c>
+      <c r="F1059">
+        <v>2</v>
+      </c>
       <c r="G1059">
         <v>0</v>
       </c>
@@ -21783,6 +23823,9 @@
       <c r="D1060" t="s">
         <v>17</v>
       </c>
+      <c r="F1060">
+        <v>0</v>
+      </c>
       <c r="G1060">
         <v>0</v>
       </c>
@@ -21803,6 +23846,9 @@
       <c r="D1061" t="s">
         <v>17</v>
       </c>
+      <c r="F1061">
+        <v>0</v>
+      </c>
       <c r="G1061">
         <v>1</v>
       </c>
@@ -21823,6 +23869,9 @@
       <c r="D1062" t="s">
         <v>17</v>
       </c>
+      <c r="F1062">
+        <v>0</v>
+      </c>
       <c r="G1062">
         <v>0</v>
       </c>
@@ -21843,6 +23892,9 @@
       <c r="D1063" t="s">
         <v>17</v>
       </c>
+      <c r="F1063">
+        <v>1</v>
+      </c>
       <c r="G1063">
         <v>0</v>
       </c>
@@ -21863,6 +23915,9 @@
       <c r="D1064" t="s">
         <v>17</v>
       </c>
+      <c r="F1064">
+        <v>0</v>
+      </c>
       <c r="G1064">
         <v>0</v>
       </c>
@@ -21883,6 +23938,9 @@
       <c r="D1065" t="s">
         <v>17</v>
       </c>
+      <c r="F1065">
+        <v>0</v>
+      </c>
       <c r="G1065">
         <v>0</v>
       </c>
@@ -21903,6 +23961,9 @@
       <c r="D1066" t="s">
         <v>18</v>
       </c>
+      <c r="F1066">
+        <v>2</v>
+      </c>
     </row>
     <row r="1067" spans="1:8">
       <c r="A1067">
@@ -21917,6 +23978,9 @@
       <c r="D1067" t="s">
         <v>18</v>
       </c>
+      <c r="F1067">
+        <v>1</v>
+      </c>
     </row>
     <row r="1068" spans="1:8">
       <c r="A1068">
@@ -21931,6 +23995,9 @@
       <c r="D1068" t="s">
         <v>18</v>
       </c>
+      <c r="F1068">
+        <v>3</v>
+      </c>
     </row>
     <row r="1069" spans="1:8">
       <c r="A1069">
@@ -21945,6 +24012,9 @@
       <c r="D1069" t="s">
         <v>18</v>
       </c>
+      <c r="F1069">
+        <v>6</v>
+      </c>
     </row>
     <row r="1070" spans="1:8">
       <c r="A1070">
@@ -21959,6 +24029,9 @@
       <c r="D1070" t="s">
         <v>18</v>
       </c>
+      <c r="F1070">
+        <v>8</v>
+      </c>
     </row>
     <row r="1071" spans="1:8">
       <c r="A1071">
@@ -21973,6 +24046,9 @@
       <c r="D1071" t="s">
         <v>18</v>
       </c>
+      <c r="F1071">
+        <v>5</v>
+      </c>
     </row>
     <row r="1072" spans="1:8">
       <c r="A1072">
@@ -21987,6 +24063,9 @@
       <c r="D1072" t="s">
         <v>18</v>
       </c>
+      <c r="F1072">
+        <v>7</v>
+      </c>
     </row>
     <row r="1073" spans="1:8">
       <c r="A1073">
@@ -22001,6 +24080,9 @@
       <c r="D1073" t="s">
         <v>18</v>
       </c>
+      <c r="F1073">
+        <v>6</v>
+      </c>
       <c r="G1073">
         <v>1</v>
       </c>
@@ -22021,6 +24103,9 @@
       <c r="D1074" t="s">
         <v>18</v>
       </c>
+      <c r="F1074">
+        <v>11</v>
+      </c>
       <c r="G1074">
         <v>3</v>
       </c>
@@ -22041,6 +24126,9 @@
       <c r="D1075" t="s">
         <v>18</v>
       </c>
+      <c r="F1075">
+        <v>7</v>
+      </c>
       <c r="G1075">
         <v>1</v>
       </c>
@@ -22061,6 +24149,9 @@
       <c r="D1076" t="s">
         <v>18</v>
       </c>
+      <c r="F1076">
+        <v>11</v>
+      </c>
       <c r="G1076">
         <v>4</v>
       </c>
@@ -22081,6 +24172,9 @@
       <c r="D1077" t="s">
         <v>18</v>
       </c>
+      <c r="F1077">
+        <v>10</v>
+      </c>
       <c r="G1077">
         <v>1</v>
       </c>
@@ -22101,6 +24195,9 @@
       <c r="D1078" t="s">
         <v>18</v>
       </c>
+      <c r="F1078">
+        <v>7</v>
+      </c>
       <c r="G1078">
         <v>4</v>
       </c>
@@ -22121,6 +24218,9 @@
       <c r="D1079" t="s">
         <v>18</v>
       </c>
+      <c r="F1079">
+        <v>16</v>
+      </c>
       <c r="G1079">
         <v>0</v>
       </c>
@@ -22141,6 +24241,9 @@
       <c r="D1080" t="s">
         <v>19</v>
       </c>
+      <c r="F1080">
+        <v>15</v>
+      </c>
     </row>
     <row r="1081" spans="1:8">
       <c r="A1081">
@@ -22155,6 +24258,9 @@
       <c r="D1081" t="s">
         <v>19</v>
       </c>
+      <c r="F1081">
+        <v>19</v>
+      </c>
     </row>
     <row r="1082" spans="1:8">
       <c r="A1082">
@@ -22169,6 +24275,9 @@
       <c r="D1082" t="s">
         <v>19</v>
       </c>
+      <c r="F1082">
+        <v>11</v>
+      </c>
     </row>
     <row r="1083" spans="1:8">
       <c r="A1083">
@@ -22183,6 +24292,9 @@
       <c r="D1083" t="s">
         <v>19</v>
       </c>
+      <c r="F1083">
+        <v>13</v>
+      </c>
     </row>
     <row r="1084" spans="1:8">
       <c r="A1084">
@@ -22197,6 +24309,9 @@
       <c r="D1084" t="s">
         <v>19</v>
       </c>
+      <c r="F1084">
+        <v>13</v>
+      </c>
     </row>
     <row r="1085" spans="1:8">
       <c r="A1085">
@@ -22211,6 +24326,9 @@
       <c r="D1085" t="s">
         <v>19</v>
       </c>
+      <c r="F1085">
+        <v>6</v>
+      </c>
     </row>
     <row r="1086" spans="1:8">
       <c r="A1086">
@@ -22225,6 +24343,9 @@
       <c r="D1086" t="s">
         <v>19</v>
       </c>
+      <c r="F1086">
+        <v>10</v>
+      </c>
     </row>
     <row r="1087" spans="1:8">
       <c r="A1087">
@@ -22239,11 +24360,14 @@
       <c r="D1087" t="s">
         <v>19</v>
       </c>
+      <c r="F1087">
+        <v>6</v>
+      </c>
       <c r="G1087">
         <v>1</v>
       </c>
       <c r="H1087">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1088" spans="1:8">
@@ -22259,6 +24383,9 @@
       <c r="D1088" t="s">
         <v>19</v>
       </c>
+      <c r="F1088">
+        <v>12</v>
+      </c>
       <c r="G1088">
         <v>0</v>
       </c>
@@ -22279,6 +24406,9 @@
       <c r="D1089" t="s">
         <v>19</v>
       </c>
+      <c r="F1089">
+        <v>8</v>
+      </c>
       <c r="G1089">
         <v>0</v>
       </c>
@@ -22299,6 +24429,9 @@
       <c r="D1090" t="s">
         <v>19</v>
       </c>
+      <c r="F1090">
+        <v>12</v>
+      </c>
       <c r="G1090">
         <v>0</v>
       </c>
@@ -22319,6 +24452,9 @@
       <c r="D1091" t="s">
         <v>19</v>
       </c>
+      <c r="F1091">
+        <v>8</v>
+      </c>
       <c r="G1091">
         <v>2</v>
       </c>
@@ -22339,6 +24475,9 @@
       <c r="D1092" t="s">
         <v>19</v>
       </c>
+      <c r="F1092">
+        <v>2</v>
+      </c>
       <c r="G1092">
         <v>1</v>
       </c>
@@ -22359,6 +24498,9 @@
       <c r="D1093" t="s">
         <v>19</v>
       </c>
+      <c r="F1093">
+        <v>7</v>
+      </c>
       <c r="G1093">
         <v>1</v>
       </c>
@@ -22379,6 +24521,9 @@
       <c r="D1094" t="s">
         <v>20</v>
       </c>
+      <c r="F1094">
+        <v>118</v>
+      </c>
     </row>
     <row r="1095" spans="1:8">
       <c r="A1095">
@@ -22393,6 +24538,9 @@
       <c r="D1095" t="s">
         <v>20</v>
       </c>
+      <c r="F1095">
+        <v>126</v>
+      </c>
     </row>
     <row r="1096" spans="1:8">
       <c r="A1096">
@@ -22407,6 +24555,9 @@
       <c r="D1096" t="s">
         <v>20</v>
       </c>
+      <c r="F1096">
+        <v>116</v>
+      </c>
     </row>
     <row r="1097" spans="1:8">
       <c r="A1097">
@@ -22421,6 +24572,9 @@
       <c r="D1097" t="s">
         <v>20</v>
       </c>
+      <c r="F1097">
+        <v>108</v>
+      </c>
     </row>
     <row r="1098" spans="1:8">
       <c r="A1098">
@@ -22435,6 +24589,9 @@
       <c r="D1098" t="s">
         <v>20</v>
       </c>
+      <c r="F1098">
+        <v>139</v>
+      </c>
     </row>
     <row r="1099" spans="1:8">
       <c r="A1099">
@@ -22449,6 +24606,9 @@
       <c r="D1099" t="s">
         <v>20</v>
       </c>
+      <c r="F1099">
+        <v>155</v>
+      </c>
     </row>
     <row r="1100" spans="1:8">
       <c r="A1100">
@@ -22463,6 +24623,9 @@
       <c r="D1100" t="s">
         <v>20</v>
       </c>
+      <c r="F1100">
+        <v>122</v>
+      </c>
     </row>
     <row r="1101" spans="1:8">
       <c r="A1101">
@@ -22477,11 +24640,14 @@
       <c r="D1101" t="s">
         <v>20</v>
       </c>
+      <c r="F1101">
+        <v>143</v>
+      </c>
       <c r="G1101">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H1101">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="1102" spans="1:8">
@@ -22497,11 +24663,14 @@
       <c r="D1102" t="s">
         <v>20</v>
       </c>
+      <c r="F1102">
+        <v>170</v>
+      </c>
       <c r="G1102">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H1102">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1103" spans="1:8">
@@ -22517,6 +24686,9 @@
       <c r="D1103" t="s">
         <v>20</v>
       </c>
+      <c r="F1103">
+        <v>129</v>
+      </c>
       <c r="G1103">
         <v>35</v>
       </c>
@@ -22537,6 +24709,9 @@
       <c r="D1104" t="s">
         <v>20</v>
       </c>
+      <c r="F1104">
+        <v>136</v>
+      </c>
       <c r="G1104">
         <v>18</v>
       </c>
@@ -22557,6 +24732,9 @@
       <c r="D1105" t="s">
         <v>20</v>
       </c>
+      <c r="F1105">
+        <v>133</v>
+      </c>
       <c r="G1105">
         <v>48</v>
       </c>
@@ -22577,6 +24755,9 @@
       <c r="D1106" t="s">
         <v>20</v>
       </c>
+      <c r="F1106">
+        <v>116</v>
+      </c>
       <c r="G1106">
         <v>50</v>
       </c>
@@ -22596,6 +24777,9 @@
       </c>
       <c r="D1107" t="s">
         <v>20</v>
+      </c>
+      <c r="F1107">
+        <v>125</v>
       </c>
       <c r="G1107">
         <v>49</v>
